--- a/output/yearly_surface_area_iteration_63_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_63_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497656512556</v>
+        <v>10.84497643647195</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907275348083</v>
+        <v>37.78907230519027</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.21740821099505</v>
+        <v>6.215444715586557</v>
       </c>
       <c r="C2" t="n">
-        <v>12.94630697590269</v>
+        <v>10.45364955482004</v>
       </c>
       <c r="D2" t="n">
-        <v>25.64128653951819</v>
+        <v>22.93755336202248</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.22891144600553</v>
+        <v>18.17705874412969</v>
       </c>
       <c r="C3" t="n">
-        <v>29.29044275620359</v>
+        <v>19.27661617288612</v>
       </c>
       <c r="D3" t="n">
-        <v>90.22261402028187</v>
+        <v>73.20401756716342</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.10573531908494</v>
+        <v>37.73936349895164</v>
       </c>
       <c r="C4" t="n">
-        <v>44.49084246105696</v>
+        <v>50.31064285183204</v>
       </c>
       <c r="D4" t="n">
-        <v>117.0213811031071</v>
+        <v>99.0004202439526</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.38757902566179</v>
+        <v>48.49833658979244</v>
       </c>
       <c r="C5" t="n">
-        <v>69.60591223109887</v>
+        <v>93.266031903447</v>
       </c>
       <c r="D5" t="n">
-        <v>87.3264582927538</v>
+        <v>76.03635969391547</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.00135126726531</v>
+        <v>47.77871552257953</v>
       </c>
       <c r="C6" t="n">
-        <v>106.344874819423</v>
+        <v>136.1311001662712</v>
       </c>
       <c r="D6" t="n">
-        <v>54.54099370943156</v>
+        <v>50.47557646614552</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.57831581772616</v>
+        <v>34.31502750653876</v>
       </c>
       <c r="C7" t="n">
-        <v>106.897598776914</v>
+        <v>132.3494080095125</v>
       </c>
       <c r="D7" t="n">
-        <v>41.20198765183014</v>
+        <v>40.06414206260808</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.43936530761284</v>
+        <v>17.94143929511046</v>
       </c>
       <c r="C8" t="n">
-        <v>71.18161729641498</v>
+        <v>84.36648896444964</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>38.2734342500619</v>
+        <v>44.37499623195582</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.670355226469191</v>
+        <v>7.65620495820644</v>
       </c>
       <c r="C21" t="n">
-        <v>94.92064592755624</v>
+        <v>92.83148511825308</v>
       </c>
       <c r="D21" t="n">
-        <v>7.670355226469191</v>
+        <v>7.65620495820644</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.425939634922874</v>
+        <v>9.343292901316895</v>
       </c>
       <c r="C2" t="n">
-        <v>9.35703736917635</v>
+        <v>6.268459091615885</v>
       </c>
       <c r="D2" t="n">
-        <v>33.99988649347554</v>
+        <v>20.78261715120073</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.61179305066178</v>
+        <v>19.32570355809846</v>
       </c>
       <c r="C3" t="n">
-        <v>39.94731408580272</v>
+        <v>29.92367002544278</v>
       </c>
       <c r="D3" t="n">
-        <v>89.32431487089605</v>
+        <v>73.92560212978482</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.82044764777662</v>
+        <v>36.11849803924015</v>
       </c>
       <c r="C4" t="n">
-        <v>58.75956359458009</v>
+        <v>49.16199803786328</v>
       </c>
       <c r="D4" t="n">
-        <v>132.6429505730823</v>
+        <v>110.895275428607</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.79915229791947</v>
+        <v>51.88536616944394</v>
       </c>
       <c r="C5" t="n">
-        <v>74.83371875621313</v>
+        <v>91.98975988792614</v>
       </c>
       <c r="D5" t="n">
-        <v>104.9733732765902</v>
+        <v>90.5416820241621</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.17243740971151</v>
+        <v>55.70829172978102</v>
       </c>
       <c r="C6" t="n">
-        <v>108.8002258277443</v>
+        <v>140.8807955594173</v>
       </c>
       <c r="D6" t="n">
-        <v>67.42152358914971</v>
+        <v>61.18251692866124</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.75903951076558</v>
+        <v>44.55563780953724</v>
       </c>
       <c r="C7" t="n">
-        <v>128.3968917522148</v>
+        <v>163.191012138426</v>
       </c>
       <c r="D7" t="n">
-        <v>46.23246288839079</v>
+        <v>44.37597797966008</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.95111790343269</v>
+        <v>26.78698611037422</v>
       </c>
       <c r="C8" t="n">
-        <v>104.6444877956675</v>
+        <v>125.5900750657732</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.87031149204818</v>
+        <v>12.53593643552752</v>
       </c>
       <c r="C9" t="n">
-        <v>61.01561981893925</v>
+        <v>72.22030636750809</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1206,7 +1206,7 @@
         <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>37.29659528433633</v>
+        <v>40.71307729511523</v>
       </c>
       <c r="D10" t="n">
         <v>35.44600086183109</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.849698826767808</v>
+        <v>7.83202651576738</v>
       </c>
       <c r="C21" t="n">
-        <v>103.0272971013275</v>
+        <v>100.837341390505</v>
       </c>
       <c r="D21" t="n">
-        <v>8.830911180113784</v>
+        <v>8.811029830238303</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.160687828326987</v>
+        <v>10.13458155093982</v>
       </c>
       <c r="C2" t="n">
-        <v>7.296348937962295</v>
+        <v>12.34155039008665</v>
       </c>
       <c r="D2" t="n">
-        <v>29.17066953628548</v>
+        <v>22.99449472886879</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.17277190041422</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="C3" t="n">
-        <v>37.93473129209675</v>
+        <v>27.08151042164826</v>
       </c>
       <c r="D3" t="n">
-        <v>93.28566685753192</v>
+        <v>72.79168353137975</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.11399021134642</v>
+        <v>35.53141291210056</v>
       </c>
       <c r="C4" t="n">
-        <v>76.44869372969913</v>
+        <v>60.50805625584366</v>
       </c>
       <c r="D4" t="n">
-        <v>141.67895644297</v>
+        <v>118.1572631969206</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.22897786593033</v>
+        <v>52.44987109938586</v>
       </c>
       <c r="C5" t="n">
-        <v>88.67636138609316</v>
+        <v>90.22261402028188</v>
       </c>
       <c r="D5" t="n">
-        <v>123.3811427312179</v>
+        <v>105.4397034361075</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.80766923208819</v>
+        <v>61.46427851978007</v>
       </c>
       <c r="C6" t="n">
-        <v>113.5499212208904</v>
+        <v>142.2493518591374</v>
       </c>
       <c r="D6" t="n">
-        <v>79.9397885660008</v>
+        <v>71.48694083243576</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>51.3228247349105</v>
+        <v>53.59851591335461</v>
       </c>
       <c r="C7" t="n">
-        <v>140.4939869639441</v>
+        <v>181.7558612257332</v>
       </c>
       <c r="D7" t="n">
-        <v>52.70021676396878</v>
+        <v>50.30475236560656</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.79666471869644</v>
+        <v>35.9663271450819</v>
       </c>
       <c r="C8" t="n">
-        <v>132.6832022289564</v>
+        <v>163.1419247532137</v>
       </c>
       <c r="D8" t="n">
-        <v>41.55738032076748</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.30624853046277</v>
+        <v>18.30468594568177</v>
       </c>
       <c r="C9" t="n">
-        <v>90.74686729434964</v>
+        <v>106.7218659378537</v>
       </c>
       <c r="D9" t="n">
         <v>36.60937189136354</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="C10" t="n">
-        <v>51.67429041303087</v>
+        <v>59.50372835439919</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>36.96083756948391</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1590,7 +1590,7 @@
         <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.013223654657651</v>
+        <v>7.993215361592882</v>
       </c>
       <c r="C21" t="n">
-        <v>111.1834782083749</v>
+        <v>108.907559301703</v>
       </c>
       <c r="D21" t="n">
-        <v>10.01652956832206</v>
+        <v>9.991519201991101</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.282023633026093</v>
+        <v>9.189158511750145</v>
       </c>
       <c r="C2" t="n">
-        <v>4.960771149559132</v>
+        <v>8.490154146326416</v>
       </c>
       <c r="D2" t="n">
-        <v>24.05281875404685</v>
+        <v>19.09401109989622</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.32556468937822</v>
+        <v>26.8998870963626</v>
       </c>
       <c r="C3" t="n">
-        <v>52.64622064023521</v>
+        <v>42.51458433240813</v>
       </c>
       <c r="D3" t="n">
-        <v>102.7104448183013</v>
+        <v>80.34623211555896</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.09150782513998</v>
+        <v>25.19360958638165</v>
       </c>
       <c r="C4" t="n">
-        <v>86.82478521588367</v>
+        <v>78.14613551034185</v>
       </c>
       <c r="D4" t="n">
-        <v>136.8291227839907</v>
+        <v>115.0303967588945</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.10944132572369</v>
+        <v>34.60660657470007</v>
       </c>
       <c r="C5" t="n">
-        <v>67.83876636345461</v>
+        <v>84.99480749516762</v>
       </c>
       <c r="D5" t="n">
-        <v>80.92055452254336</v>
+        <v>71.05399009486291</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.83905979642831</v>
+        <v>33.24786775202249</v>
       </c>
       <c r="C6" t="n">
-        <v>92.53855685460012</v>
+        <v>119.7084245696306</v>
       </c>
       <c r="D6" t="n">
-        <v>34.69692736349078</v>
+        <v>33.12711278440013</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.39759212468673</v>
+        <v>23.83487076370406</v>
       </c>
       <c r="C7" t="n">
-        <v>93.30333831620835</v>
+        <v>114.6828580715911</v>
       </c>
       <c r="D7" t="n">
-        <v>29.22466566001905</v>
+        <v>28.38625312059227</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.01659189998096</v>
+        <v>12.68418033886879</v>
       </c>
       <c r="C8" t="n">
-        <v>66.84229244364408</v>
+        <v>78.60853867904211</v>
       </c>
       <c r="D8" t="n">
         <v>26.95388322009618</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>39.38280915586078</v>
+        <v>45.37343364717482</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>28.18597658892593</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>26.4698816019025</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -1887,7 +1887,7 @@
         <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.977460860531329</v>
+        <v>5.39863062565321</v>
       </c>
       <c r="C2" t="n">
-        <v>2.487748682561417</v>
+        <v>4.315762907868979</v>
       </c>
       <c r="D2" t="n">
-        <v>17.06179335210532</v>
+        <v>13.39300218133499</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.0534406488526</v>
+        <v>29.8254952550181</v>
       </c>
       <c r="C3" t="n">
-        <v>36.39829613495049</v>
+        <v>38.53850613020854</v>
       </c>
       <c r="D3" t="n">
-        <v>100.1628095257808</v>
+        <v>78.54472507826607</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.85048091598077</v>
+        <v>36.34822700203391</v>
       </c>
       <c r="C4" t="n">
-        <v>110.5762074247267</v>
+        <v>94.44412914854315</v>
       </c>
       <c r="D4" t="n">
-        <v>152.7314720973805</v>
+        <v>126.1467260140812</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.88916998707391</v>
+        <v>38.11635461738242</v>
       </c>
       <c r="C5" t="n">
-        <v>110.5938788834032</v>
+        <v>112.8028112179585</v>
       </c>
       <c r="D5" t="n">
-        <v>102.7398972494287</v>
+        <v>88.99542938997337</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.43403996293088</v>
+        <v>39.28561613314037</v>
       </c>
       <c r="C6" t="n">
-        <v>104.6140536168359</v>
+        <v>133.7965041255723</v>
       </c>
       <c r="D6" t="n">
-        <v>44.67933802027235</v>
+        <v>41.70071548558752</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.08008670558751</v>
+        <v>22.21793229480956</v>
       </c>
       <c r="C7" t="n">
-        <v>112.2873936732289</v>
+        <v>140.3742137440259</v>
       </c>
       <c r="D7" t="n">
-        <v>32.09922293805371</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>87.45408549430587</v>
+        <v>103.9768993567797</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>27.70492021384499</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>44.26405874137593</v>
+        <v>50.36562072326985</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.06718511671205</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.98040610364407</v>
+        <v>5.813909904549611</v>
       </c>
       <c r="C2" t="n">
-        <v>3.738495257771854</v>
+        <v>7.395505456091222</v>
       </c>
       <c r="D2" t="n">
-        <v>21.90377302945059</v>
+        <v>10.7884255219682</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.65873701401638</v>
+        <v>24.27371198750239</v>
       </c>
       <c r="C3" t="n">
-        <v>22.29549036344507</v>
+        <v>27.1011453757332</v>
       </c>
       <c r="D3" t="n">
-        <v>91.41052874242052</v>
+        <v>71.6872173641021</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.10796085640069</v>
+        <v>45.97131799906114</v>
       </c>
       <c r="C4" t="n">
-        <v>100.4681330618016</v>
+        <v>95.28646867878692</v>
       </c>
       <c r="D4" t="n">
-        <v>165.6601076146068</v>
+        <v>135.0423419622615</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.71860792844222</v>
+        <v>45.74944301790137</v>
       </c>
       <c r="C5" t="n">
-        <v>156.2942345160922</v>
+        <v>143.8996697499763</v>
       </c>
       <c r="D5" t="n">
-        <v>128.9280172602124</v>
+        <v>109.8575681052181</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.63279496754524</v>
+        <v>45.44411948188061</v>
       </c>
       <c r="C6" t="n">
-        <v>139.2304776685784</v>
+        <v>155.0896300829814</v>
       </c>
       <c r="D6" t="n">
-        <v>61.90704673439538</v>
+        <v>56.15105994439633</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.24273802932299</v>
+        <v>31.79978988825843</v>
       </c>
       <c r="C7" t="n">
-        <v>131.9900883497582</v>
+        <v>166.9638685658466</v>
       </c>
       <c r="D7" t="n">
-        <v>36.47094546506476</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.77039421039326</v>
+        <v>15.60487975900305</v>
       </c>
       <c r="C8" t="n">
-        <v>115.9934912567606</v>
+        <v>141.6956461539421</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>71.44374393344886</v>
+        <v>83.53593040665682</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>43.98720588877834</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.961932823712627</v>
+        <v>3.447897937314798</v>
       </c>
       <c r="C2" t="n">
-        <v>1.796598298771663</v>
+        <v>3.445934441906304</v>
       </c>
       <c r="D2" t="n">
-        <v>15.31428243854599</v>
+        <v>7.547676350249478</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.37893891830604</v>
+        <v>24.52896639060656</v>
       </c>
       <c r="C3" t="n">
-        <v>20.40562603276996</v>
+        <v>29.5947845445201</v>
       </c>
       <c r="D3" t="n">
-        <v>91.24363163269857</v>
+        <v>68.23146544515332</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.89398091460389</v>
+        <v>51.08916878129977</v>
       </c>
       <c r="C4" t="n">
-        <v>94.15058658497337</v>
+        <v>94.3420273873015</v>
       </c>
       <c r="D4" t="n">
-        <v>175.4363512534965</v>
+        <v>142.3936687716616</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.80482179996669</v>
+        <v>48.15472489330606</v>
       </c>
       <c r="C5" t="n">
-        <v>185.9921025695583</v>
+        <v>173.1802950291374</v>
       </c>
       <c r="D5" t="n">
-        <v>135.7757074973339</v>
+        <v>115.5762484824558</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.50825187782615</v>
+        <v>38.19882142453915</v>
       </c>
       <c r="C6" t="n">
-        <v>172.1965838294821</v>
+        <v>193.1676965398982</v>
       </c>
       <c r="D6" t="n">
-        <v>59.97496725243766</v>
+        <v>54.78250364467628</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.761517423326035</v>
+        <v>10.30049691295753</v>
       </c>
       <c r="C7" t="n">
-        <v>144.2069567814055</v>
+        <v>180.0191495369206</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>87.87132826861075</v>
+        <v>104.5610392408065</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>33.50312215512664</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.28437234352885</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.2780555844801</v>
+        <v>4.515057691831081</v>
       </c>
       <c r="C2" t="n">
-        <v>5.095270585040946</v>
+        <v>2.899100970640831</v>
       </c>
       <c r="D2" t="n">
-        <v>15.95929068023615</v>
+        <v>9.242172887779473</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.48354395430395</v>
+        <v>18.39795197758523</v>
       </c>
       <c r="C3" t="n">
-        <v>13.58247948825462</v>
+        <v>21.3775562599743</v>
       </c>
       <c r="D3" t="n">
-        <v>83.98851609831463</v>
+        <v>59.49881961587794</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.98408071921636</v>
+        <v>49.0471335564664</v>
       </c>
       <c r="C4" t="n">
-        <v>72.84960664593032</v>
+        <v>84.19566486391069</v>
       </c>
       <c r="D4" t="n">
-        <v>179.5842353039393</v>
+        <v>145.1376536050315</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.24218255444204</v>
+        <v>60.37748381117885</v>
       </c>
       <c r="C5" t="n">
-        <v>181.6724126708723</v>
+        <v>174.9474408967816</v>
       </c>
       <c r="D5" t="n">
-        <v>160.6630117999905</v>
+        <v>134.8430471782994</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.2956956520901</v>
+        <v>49.10702016642546</v>
       </c>
       <c r="C6" t="n">
-        <v>228.3878954297525</v>
+        <v>231.6482795555562</v>
       </c>
       <c r="D6" t="n">
-        <v>81.02658327460202</v>
+        <v>72.17121898229578</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.66088043587412</v>
+        <v>21.55917958525995</v>
       </c>
       <c r="C7" t="n">
-        <v>191.9365849187727</v>
+        <v>226.6109320850658</v>
       </c>
       <c r="D7" t="n">
-        <v>42.75903951076558</v>
+        <v>40.90255460203486</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>130.513539802571</v>
+        <v>159.5536368941916</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>59.68436993198057</v>
+        <v>68.55936917837174</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.48478774391545</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.407245370813179</v>
+        <v>3.058144098728814</v>
       </c>
       <c r="C2" t="n">
-        <v>2.86866679180918</v>
+        <v>1.944842202112931</v>
       </c>
       <c r="D2" t="n">
-        <v>12.75879316439155</v>
+        <v>6.971390447856601</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.41696503686441</v>
+        <v>17.29348581030757</v>
       </c>
       <c r="C3" t="n">
-        <v>16.73388961888688</v>
+        <v>17.11677122354314</v>
       </c>
       <c r="D3" t="n">
-        <v>78.91288046735862</v>
+        <v>54.6637121724624</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.1214843400819</v>
+        <v>44.4015034199705</v>
       </c>
       <c r="C4" t="n">
-        <v>57.59815606045612</v>
+        <v>72.51777592189489</v>
       </c>
       <c r="D4" t="n">
-        <v>181.0519481217883</v>
+        <v>143.4019236639231</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.13266877992289</v>
+        <v>67.00428081484482</v>
       </c>
       <c r="C5" t="n">
-        <v>169.6950906790612</v>
+        <v>173.2539261069559</v>
       </c>
       <c r="D5" t="n">
-        <v>180.1261600366836</v>
+        <v>149.9374181310941</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.74854338565514</v>
+        <v>57.88188114698346</v>
       </c>
       <c r="C6" t="n">
-        <v>259.3816704528243</v>
+        <v>258.3753790559714</v>
       </c>
       <c r="D6" t="n">
-        <v>97.36875555949442</v>
+        <v>85.5750203883775</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.28348840681585</v>
+        <v>20.12190094624263</v>
       </c>
       <c r="C7" t="n">
-        <v>241.2232649150752</v>
+        <v>270.9270234547668</v>
       </c>
       <c r="D7" t="n">
-        <v>49.22679338634357</v>
+        <v>46.65166915810418</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>165.1446900698772</v>
+        <v>200.0261860017664</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>69.77968157475051</v>
+        <v>80.09686819868024</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.456733666653019</v>
+        <v>4.102723656047421</v>
       </c>
       <c r="C2" t="n">
-        <v>5.614615120587509</v>
+        <v>3.026728172192916</v>
       </c>
       <c r="D2" t="n">
-        <v>15.25832281940393</v>
+        <v>9.109636947706154</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.42263453891164</v>
+        <v>13.95554361586841</v>
       </c>
       <c r="C3" t="n">
-        <v>14.15680189523901</v>
+        <v>12.53691818323177</v>
       </c>
       <c r="D3" t="n">
-        <v>72.04555527615217</v>
+        <v>48.78795216254525</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.61249706092554</v>
+        <v>38.74761839121312</v>
       </c>
       <c r="C4" t="n">
-        <v>50.43827005338413</v>
+        <v>58.89995351628739</v>
       </c>
       <c r="D4" t="n">
-        <v>179.0099128969549</v>
+        <v>138.8583952886689</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.78905708343652</v>
+        <v>67.44606728175589</v>
       </c>
       <c r="C5" t="n">
-        <v>142.4025045009999</v>
+        <v>155.680642200938</v>
       </c>
       <c r="D5" t="n">
-        <v>197.2331137831843</v>
+        <v>162.2828955119978</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.18001365390501</v>
+        <v>69.43410638285567</v>
       </c>
       <c r="C6" t="n">
-        <v>264.4533790929634</v>
+        <v>268.8005579273682</v>
       </c>
       <c r="D6" t="n">
-        <v>119.8694311931271</v>
+        <v>103.648013875857</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.7941203862112</v>
+        <v>37.00992495469625</v>
       </c>
       <c r="C7" t="n">
-        <v>295.001440658307</v>
+        <v>313.0273102559827</v>
       </c>
       <c r="D7" t="n">
-        <v>60.90468232835937</v>
+        <v>56.41318658143022</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>226.9800692218625</v>
+        <v>262.5291535926395</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>118.1484274675824</v>
+        <v>142.6656128857379</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>49.68134257340984</v>
+        <v>53.80959166976768</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
         <v>24.87748682561417</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.715154297048183</v>
+        <v>7.949211161286423</v>
       </c>
       <c r="C2" t="n">
-        <v>5.008876787067226</v>
+        <v>8.638398049667684</v>
       </c>
       <c r="D2" t="n">
-        <v>11.49626561673015</v>
+        <v>15.56266460772044</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.475967710110456</v>
+        <v>2.938370878810703</v>
       </c>
       <c r="C2" t="n">
-        <v>3.189698291097887</v>
+        <v>1.719040230136165</v>
       </c>
       <c r="D2" t="n">
-        <v>11.22923024117502</v>
+        <v>6.705336820005715</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.44780012632356</v>
+        <v>18.39304323906399</v>
       </c>
       <c r="C3" t="n">
-        <v>18.60411899547706</v>
+        <v>14.22061549601505</v>
       </c>
       <c r="D3" t="n">
-        <v>78.67235227981814</v>
+        <v>53.33835277172921</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.3068957874643</v>
+        <v>52.22505087511333</v>
       </c>
       <c r="C4" t="n">
-        <v>75.04479451262618</v>
+        <v>84.84656359182634</v>
       </c>
       <c r="D4" t="n">
-        <v>183.4385767908123</v>
+        <v>143.4146863840783</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.61351986635881</v>
+        <v>40.98796665230434</v>
       </c>
       <c r="C5" t="n">
-        <v>219.3715245139498</v>
+        <v>230.1216618754524</v>
       </c>
       <c r="D5" t="n">
-        <v>179.7089172623787</v>
+        <v>149.3483695085461</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.57488754852791</v>
+        <v>22.98369550412208</v>
       </c>
       <c r="C6" t="n">
-        <v>246.1388756702391</v>
+        <v>258.8583989264608</v>
       </c>
       <c r="D6" t="n">
-        <v>93.62535156320133</v>
+        <v>83.07941772418209</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.407867265618931</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>159.5978155408827</v>
+        <v>184.6304185037679</v>
       </c>
       <c r="D7" t="n">
-        <v>34.49468733641593</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>87.03684272000096</v>
+        <v>105.1451791248334</v>
       </c>
       <c r="D8" t="n">
-        <v>24.78422079371073</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>37.94062177832222</v>
+        <v>41.04687151455913</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>19.96874830438012</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.92242623583128</v>
       </c>
       <c r="D10" t="n">
         <v>19.50241814486289</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.372925258893546</v>
+        <v>7.701810739816227</v>
       </c>
       <c r="C2" t="n">
-        <v>9.530806712828035</v>
+        <v>7.316965639751478</v>
       </c>
       <c r="D2" t="n">
-        <v>26.20186447864312</v>
+        <v>20.32512272102171</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.25988540418492</v>
+        <v>16.87624303600267</v>
       </c>
       <c r="C3" t="n">
-        <v>12.62036673809275</v>
+        <v>21.76534660315179</v>
       </c>
       <c r="D3" t="n">
-        <v>12.79217258633594</v>
+        <v>16.20865459711484</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39801560623912</v>
+        <v>13.39648557404594</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14255229148716</v>
+        <v>70.13454212294641</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576237130145779</v>
+        <v>1.576057126358346</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.288674882777567</v>
+        <v>5.393721887131976</v>
       </c>
       <c r="C2" t="n">
-        <v>5.352488483553611</v>
+        <v>9.364891350810323</v>
       </c>
       <c r="D2" t="n">
-        <v>37.21805546799659</v>
+        <v>22.16295442337174</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.98976591679681</v>
+        <v>22.75691178444107</v>
       </c>
       <c r="C3" t="n">
-        <v>27.9798095710341</v>
+        <v>26.00158794697677</v>
       </c>
       <c r="D3" t="n">
-        <v>31.71045084717197</v>
+        <v>29.3640738340221</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.54048532115026</v>
+        <v>19.50143639715864</v>
       </c>
       <c r="C4" t="n">
-        <v>19.79497896072844</v>
+        <v>33.71910665006095</v>
       </c>
       <c r="D4" t="n">
-        <v>21.77320058478576</v>
+        <v>23.55998140651495</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
@@ -4927,7 +4927,7 @@
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.36098972218912</v>
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43851734820239</v>
+        <v>15.43550097857097</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13067573207648</v>
+        <v>86.1138475646591</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250214178568924</v>
+        <v>3.249579153383362</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.544911033585985</v>
+        <v>5.980807014271569</v>
       </c>
       <c r="C2" t="n">
-        <v>4.120395114723864</v>
+        <v>6.304783756673016</v>
       </c>
       <c r="D2" t="n">
-        <v>28.18695833663017</v>
+        <v>24.42097414313941</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.66440651606361</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="C3" t="n">
-        <v>23.69448084199677</v>
+        <v>32.20623343781661</v>
       </c>
       <c r="D3" t="n">
-        <v>54.12375093512666</v>
+        <v>40.28110830524663</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.77542612210151</v>
+        <v>32.99163160121406</v>
       </c>
       <c r="C4" t="n">
-        <v>48.85569275413827</v>
+        <v>51.8804574309227</v>
       </c>
       <c r="D4" t="n">
-        <v>32.7491399182651</v>
+        <v>32.96610616090365</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.28442909679109</v>
+        <v>16.56699250916493</v>
       </c>
       <c r="C5" t="n">
-        <v>22.82563412373834</v>
+        <v>37.23278168356029</v>
       </c>
       <c r="D5" t="n">
-        <v>30.48326621686347</v>
+        <v>31.39138284329177</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.9695754878309</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.57727731675966</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72585435227503</v>
+        <v>16.72176227104086</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0277115488777</v>
+        <v>102.0027498533492</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181463588068757</v>
+        <v>4.180440567760215</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.258240703945916</v>
+        <v>5.639158813193679</v>
       </c>
       <c r="C2" t="n">
-        <v>3.795436624618169</v>
+        <v>4.628940425523711</v>
       </c>
       <c r="D2" t="n">
-        <v>22.24345773511998</v>
+        <v>24.28941995077033</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.24716374175872</v>
+        <v>20.40562603276996</v>
       </c>
       <c r="C3" t="n">
-        <v>19.29625112697106</v>
+        <v>27.78346003018473</v>
       </c>
       <c r="D3" t="n">
-        <v>63.50435024920493</v>
+        <v>49.8776921142592</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.98712377332033</v>
+        <v>36.55243052451725</v>
       </c>
       <c r="C4" t="n">
-        <v>54.10117073792898</v>
+        <v>67.61689138229482</v>
       </c>
       <c r="D4" t="n">
-        <v>51.44652494564561</v>
+        <v>45.05240214788613</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.45243112740432</v>
+        <v>32.49584901056943</v>
       </c>
       <c r="C5" t="n">
-        <v>59.19938656608268</v>
+        <v>67.91239744127311</v>
       </c>
       <c r="D5" t="n">
-        <v>34.87658719336795</v>
+        <v>35.66198535676539</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.47801332097696</v>
+        <v>14.00757624419349</v>
       </c>
       <c r="C6" t="n">
-        <v>24.67426505083509</v>
+        <v>36.50825187782615</v>
       </c>
       <c r="D6" t="n">
-        <v>38.35982804803563</v>
+        <v>38.23907308041327</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.2097595180061</v>
       </c>
       <c r="D8" t="n">
         <v>39.30426933952106</v>
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>48.54251523648354</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.6434553235717</v>
       </c>
     </row>
     <row r="12">
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
         <v>34.28066633689012</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0436997566574</v>
+        <v>18.03609024224323</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7136603172411</v>
+        <v>117.6640172946344</v>
       </c>
       <c r="D21" t="n">
-        <v>6.014566585552467</v>
+        <v>6.012030080747745</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.223298697220531</v>
+        <v>6.660176425610362</v>
       </c>
       <c r="C2" t="n">
-        <v>3.25645713498667</v>
+        <v>4.0938879267092</v>
       </c>
       <c r="D2" t="n">
-        <v>34.57028190964293</v>
+        <v>28.3783991389583</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.50317890838888</v>
+        <v>17.5291052593268</v>
       </c>
       <c r="C3" t="n">
-        <v>15.68832831386403</v>
+        <v>20.87195619228719</v>
       </c>
       <c r="D3" t="n">
-        <v>62.36552291227864</v>
+        <v>53.85377031645879</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.09976271740145</v>
+        <v>27.46537377400877</v>
       </c>
       <c r="C4" t="n">
-        <v>42.10421379203296</v>
+        <v>57.35566437750716</v>
       </c>
       <c r="D4" t="n">
-        <v>61.63117562950202</v>
+        <v>51.57415214719769</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.51914891356409</v>
+        <v>26.80171232593793</v>
       </c>
       <c r="C5" t="n">
-        <v>60.20567796293566</v>
+        <v>72.18299995474675</v>
       </c>
       <c r="D5" t="n">
-        <v>36.07922813107029</v>
+        <v>35.12202411942965</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.28933783531233</v>
+        <v>15.53713916741002</v>
       </c>
       <c r="C6" t="n">
-        <v>40.53341746523807</v>
+        <v>49.46928506929254</v>
       </c>
       <c r="D6" t="n">
-        <v>31.63780151705772</v>
+        <v>31.27553661419064</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.809001166028376</v>
+        <v>6.228207435741766</v>
       </c>
       <c r="C7" t="n">
-        <v>18.38518925743002</v>
+        <v>23.53543771390878</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.67707142522758</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5955,7 +5955,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
         <v>26.03889435973815</v>
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.049625961617508</v>
+        <v>7.044268132665879</v>
       </c>
       <c r="C21" t="n">
-        <v>66.97144663536632</v>
+        <v>66.04001374374262</v>
       </c>
       <c r="D21" t="n">
-        <v>4.406016226010943</v>
+        <v>4.402667582916174</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.602834148136546</v>
+        <v>5.717698629533423</v>
       </c>
       <c r="C2" t="n">
-        <v>6.439283192154829</v>
+        <v>6.005350706877739</v>
       </c>
       <c r="D2" t="n">
-        <v>33.61209615029805</v>
+        <v>27.14041528390307</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.68895020866978</v>
+        <v>21.01921834792421</v>
       </c>
       <c r="C3" t="n">
-        <v>13.77392029058275</v>
+        <v>17.76472470834603</v>
       </c>
       <c r="D3" t="n">
-        <v>76.33579274371074</v>
+        <v>64.67753875577988</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.9030533236536</v>
+        <v>31.88127494771092</v>
       </c>
       <c r="C4" t="n">
-        <v>40.43229745170064</v>
+        <v>54.31813698056752</v>
       </c>
       <c r="D4" t="n">
-        <v>79.42240752586271</v>
+        <v>67.83385762493337</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.35487825178539</v>
+        <v>35.12202411942965</v>
       </c>
       <c r="C5" t="n">
-        <v>71.10307748007526</v>
+        <v>92.62789589568656</v>
       </c>
       <c r="D5" t="n">
-        <v>51.5908418581699</v>
+        <v>45.99487994396307</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.19753657719864</v>
+        <v>27.49188096202344</v>
       </c>
       <c r="C6" t="n">
-        <v>72.97625209977816</v>
+        <v>86.74231840872694</v>
       </c>
       <c r="D6" t="n">
-        <v>36.46800022195202</v>
+        <v>35.86422538384024</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.0970952117292</v>
+        <v>13.1750541909922</v>
       </c>
       <c r="C7" t="n">
-        <v>41.74096714146164</v>
+        <v>51.44259795482861</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>22.28076414788136</v>
+        <v>26.20284622634736</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
         <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6308,7 +6308,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.269199903685337</v>
+        <v>7.261498152136733</v>
       </c>
       <c r="C21" t="n">
-        <v>76.32659898869603</v>
+        <v>75.33804332841861</v>
       </c>
       <c r="D21" t="n">
-        <v>5.451899927764003</v>
+        <v>5.446123614102549</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.153594610219008</v>
+        <v>4.830198704894307</v>
       </c>
       <c r="C2" t="n">
-        <v>9.373727080148546</v>
+        <v>4.60439673291754</v>
       </c>
       <c r="D2" t="n">
-        <v>31.81549785152638</v>
+        <v>23.62870374581223</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.53677931451153</v>
+        <v>20.28781630826034</v>
       </c>
       <c r="C3" t="n">
-        <v>20.48907458763093</v>
+        <v>21.09284942574272</v>
       </c>
       <c r="D3" t="n">
-        <v>85.51513377841843</v>
+        <v>71.38287557578558</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.86775146402972</v>
+        <v>37.01188845010475</v>
       </c>
       <c r="C4" t="n">
-        <v>36.6290068454485</v>
+        <v>48.65148923165493</v>
       </c>
       <c r="D4" t="n">
-        <v>99.85552249435158</v>
+        <v>85.02524167399926</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.66260725157115</v>
+        <v>41.87153958612647</v>
       </c>
       <c r="C5" t="n">
-        <v>73.26292242941824</v>
+        <v>97.04576056479723</v>
       </c>
       <c r="D5" t="n">
-        <v>67.96148482648546</v>
+        <v>59.98478472948013</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.26674194258143</v>
+        <v>38.15856976866503</v>
       </c>
       <c r="C6" t="n">
-        <v>95.15491448641787</v>
+        <v>119.5474179461341</v>
       </c>
       <c r="D6" t="n">
-        <v>44.71958967614647</v>
+        <v>41.82147045320988</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.55917958525995</v>
+        <v>23.65521093382689</v>
       </c>
       <c r="C7" t="n">
-        <v>76.41531430775473</v>
+        <v>90.4287810381737</v>
       </c>
       <c r="D7" t="n">
-        <v>36.65060529494193</v>
+        <v>36.83026512481909</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>39.97185777840888</v>
+        <v>48.90085314853362</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>33.21252483466959</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>26.18124777685393</v>
+        <v>28.73281006019139</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6619,7 +6619,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.476606130218818</v>
+        <v>7.465706206314437</v>
       </c>
       <c r="C21" t="n">
-        <v>85.98097049751641</v>
+        <v>83.98919482103742</v>
       </c>
       <c r="D21" t="n">
-        <v>6.542030363941466</v>
+        <v>6.532492930525132</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_63_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_63_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497643647195</v>
+        <v>10.84497624594625</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907230519027</v>
+        <v>37.78907164130779</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.215444715586557</v>
+        <v>8.430267536367362</v>
       </c>
       <c r="C2" t="n">
-        <v>10.45364955482004</v>
+        <v>6.034803138005143</v>
       </c>
       <c r="D2" t="n">
-        <v>22.93755336202248</v>
+        <v>36.0252320073367</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.17705874412969</v>
+        <v>25.32418203104648</v>
       </c>
       <c r="C3" t="n">
-        <v>19.27661617288612</v>
+        <v>29.34443887993716</v>
       </c>
       <c r="D3" t="n">
-        <v>73.20401756716342</v>
+        <v>69.39483647468579</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.73936349895164</v>
+        <v>53.27159392784043</v>
       </c>
       <c r="C4" t="n">
-        <v>50.31064285183204</v>
+        <v>90.9088556655504</v>
       </c>
       <c r="D4" t="n">
-        <v>99.0004202439526</v>
+        <v>86.17388648796803</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.49833658979244</v>
+        <v>62.58641614573418</v>
       </c>
       <c r="C5" t="n">
-        <v>93.266031903447</v>
+        <v>124.0929098167969</v>
       </c>
       <c r="D5" t="n">
-        <v>76.03635969391547</v>
+        <v>68.79597037509525</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.77871552257953</v>
+        <v>53.61520562432682</v>
       </c>
       <c r="C6" t="n">
-        <v>136.1311001662712</v>
+        <v>99.34108669732626</v>
       </c>
       <c r="D6" t="n">
-        <v>50.47557646614552</v>
+        <v>47.41645061971246</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.31502750653876</v>
+        <v>37.42913122440964</v>
       </c>
       <c r="C7" t="n">
-        <v>132.3494080095125</v>
+        <v>77.97236616669016</v>
       </c>
       <c r="D7" t="n">
-        <v>40.06414206260808</v>
+        <v>39.34550274309942</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.94143929511046</v>
+        <v>19.19316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>84.36648896444964</v>
+        <v>51.40430979436299</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.209374302911826</v>
+        <v>8.653124265231384</v>
       </c>
       <c r="C9" t="n">
-        <v>44.37499623195582</v>
+        <v>32.50468473990763</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.65620495820644</v>
+        <v>7.691238419923476</v>
       </c>
       <c r="C21" t="n">
-        <v>92.83148511825308</v>
+        <v>94.21767064406257</v>
       </c>
       <c r="D21" t="n">
-        <v>7.65620495820644</v>
+        <v>8.652643222413911</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.343292901316895</v>
+        <v>9.425759708473628</v>
       </c>
       <c r="C2" t="n">
-        <v>6.268459091615885</v>
+        <v>10.31915011933822</v>
       </c>
       <c r="D2" t="n">
-        <v>20.78261715120073</v>
+        <v>26.96860943565988</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.32570355809846</v>
+        <v>26.55136666135499</v>
       </c>
       <c r="C3" t="n">
-        <v>29.92367002544278</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D3" t="n">
-        <v>73.92560212978482</v>
+        <v>79.78663592413828</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.11849803924015</v>
+        <v>50.22130381074558</v>
       </c>
       <c r="C4" t="n">
-        <v>49.16199803786328</v>
+        <v>81.26023922821274</v>
       </c>
       <c r="D4" t="n">
-        <v>110.895275428607</v>
+        <v>98.92384392302137</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.88536616944394</v>
+        <v>70.75946578358887</v>
       </c>
       <c r="C5" t="n">
-        <v>91.98975988792614</v>
+        <v>144.8814174542231</v>
       </c>
       <c r="D5" t="n">
-        <v>90.5416820241621</v>
+        <v>80.92055452254336</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.70829172978102</v>
+        <v>67.22026530977911</v>
       </c>
       <c r="C6" t="n">
-        <v>140.8807955594173</v>
+        <v>143.3763982236127</v>
       </c>
       <c r="D6" t="n">
-        <v>61.18251692866124</v>
+        <v>56.79508643838223</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.55563780953724</v>
+        <v>49.34656660626167</v>
       </c>
       <c r="C7" t="n">
-        <v>163.191012138426</v>
+        <v>108.6941970756856</v>
       </c>
       <c r="D7" t="n">
-        <v>44.37597797966008</v>
+        <v>43.11835917051991</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.78698611037422</v>
+        <v>28.87319998189869</v>
       </c>
       <c r="C8" t="n">
-        <v>125.5900750657732</v>
+        <v>74.93680226515903</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.53593643552752</v>
+        <v>13.53437385074652</v>
       </c>
       <c r="C9" t="n">
-        <v>72.22030636750809</v>
+        <v>47.14843349645305</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>40.71307729511523</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.83202651576738</v>
+        <v>7.869033539789666</v>
       </c>
       <c r="C21" t="n">
-        <v>100.837341390505</v>
+        <v>102.2974360172657</v>
       </c>
       <c r="D21" t="n">
-        <v>8.811029830238303</v>
+        <v>9.836291924737083</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.13458155093982</v>
+        <v>11.6356737907332</v>
       </c>
       <c r="C2" t="n">
-        <v>12.34155039008665</v>
+        <v>12.44757914214531</v>
       </c>
       <c r="D2" t="n">
-        <v>22.99449472886879</v>
+        <v>20.90239037111884</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.20008090968388</v>
+        <v>28.20070280448963</v>
       </c>
       <c r="C3" t="n">
-        <v>27.08151042164826</v>
+        <v>32.40258297866598</v>
       </c>
       <c r="D3" t="n">
-        <v>72.79168353137975</v>
+        <v>81.28380117311467</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.53141291210056</v>
+        <v>49.13647259755286</v>
       </c>
       <c r="C4" t="n">
-        <v>60.50805625584366</v>
+        <v>73.88338697850222</v>
       </c>
       <c r="D4" t="n">
-        <v>118.1572631969206</v>
+        <v>110.588970144882</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.44987109938586</v>
+        <v>72.10936887692823</v>
       </c>
       <c r="C5" t="n">
-        <v>90.22261402028188</v>
+        <v>145.1759417654971</v>
       </c>
       <c r="D5" t="n">
-        <v>105.4397034361075</v>
+        <v>94.19869222248147</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.46427851978007</v>
+        <v>78.49072895453251</v>
       </c>
       <c r="C6" t="n">
-        <v>142.2493518591374</v>
+        <v>178.6771004252153</v>
       </c>
       <c r="D6" t="n">
-        <v>71.48694083243576</v>
+        <v>65.69070238656259</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>53.59851591335461</v>
+        <v>61.92275469766331</v>
       </c>
       <c r="C7" t="n">
-        <v>181.7558612257332</v>
+        <v>150.6747106569835</v>
       </c>
       <c r="D7" t="n">
-        <v>50.30475236560656</v>
+        <v>48.32849423695774</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>35.9663271450819</v>
+        <v>39.30426933952106</v>
       </c>
       <c r="C8" t="n">
-        <v>163.1419247532137</v>
+        <v>103.3927594727528</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.30468594568177</v>
+        <v>19.74687332322034</v>
       </c>
       <c r="C9" t="n">
-        <v>106.7218659378537</v>
+        <v>66.11874438561416</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.683558444063038</v>
+        <v>9.252972112526189</v>
       </c>
       <c r="C10" t="n">
-        <v>59.50372835439919</v>
+        <v>43.2754388031994</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>38.20471191076462</v>
+        <v>35.18387422479719</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
         <v>36.01639627799849</v>
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1573,7 +1573,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.993215361592882</v>
+        <v>8.030614307722326</v>
       </c>
       <c r="C21" t="n">
-        <v>108.907559301703</v>
+        <v>110.420946731182</v>
       </c>
       <c r="D21" t="n">
-        <v>9.991519201991101</v>
+        <v>11.0420946731182</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.189158511750145</v>
+        <v>10.57145927932965</v>
       </c>
       <c r="C2" t="n">
-        <v>8.490154146326416</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="D2" t="n">
-        <v>19.09401109989622</v>
+        <v>17.50161632360789</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.8998870963626</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="C3" t="n">
-        <v>42.51458433240813</v>
+        <v>49.80406103644069</v>
       </c>
       <c r="D3" t="n">
-        <v>80.34623211555896</v>
+        <v>87.19392235268047</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.19360958638165</v>
+        <v>34.63802250123597</v>
       </c>
       <c r="C4" t="n">
-        <v>78.14613551034185</v>
+        <v>112.8990224929747</v>
       </c>
       <c r="D4" t="n">
-        <v>115.0303967588945</v>
+        <v>106.0454417696277</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.60660657470007</v>
+        <v>44.20319038371264</v>
       </c>
       <c r="C5" t="n">
-        <v>84.99480749516762</v>
+        <v>106.7650628368407</v>
       </c>
       <c r="D5" t="n">
-        <v>71.05399009486291</v>
+        <v>64.57445524683396</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.24786775202249</v>
+        <v>38.44033135978387</v>
       </c>
       <c r="C6" t="n">
-        <v>119.7084245696306</v>
+        <v>99.22033172970391</v>
       </c>
       <c r="D6" t="n">
-        <v>33.12711278440013</v>
+        <v>31.79880814055419</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.83487076370406</v>
+        <v>26.05067533218911</v>
       </c>
       <c r="C7" t="n">
-        <v>114.6828580715911</v>
+        <v>72.7023444902933</v>
       </c>
       <c r="D7" t="n">
-        <v>28.38625312059227</v>
+        <v>28.32636651063322</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>13.68556299720053</v>
       </c>
       <c r="C8" t="n">
-        <v>78.60853867904211</v>
+        <v>48.73395603881166</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>45.37343364717482</v>
+        <v>32.9484347022272</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>28.18597658892593</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
         <v>28.78680618392497</v>
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>26.4698816019025</v>
@@ -1870,7 +1870,7 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.39863062565321</v>
+        <v>6.409830761027425</v>
       </c>
       <c r="C2" t="n">
-        <v>4.315762907868979</v>
+        <v>4.241150082346221</v>
       </c>
       <c r="D2" t="n">
-        <v>13.39300218133499</v>
+        <v>12.39751000922872</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.8254952550181</v>
+        <v>35.96141840656067</v>
       </c>
       <c r="C3" t="n">
-        <v>38.53850613020854</v>
+        <v>42.32805226860123</v>
       </c>
       <c r="D3" t="n">
-        <v>78.54472507826607</v>
+        <v>82.2115527536279</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.34822700203391</v>
+        <v>47.64323433939346</v>
       </c>
       <c r="C4" t="n">
-        <v>94.44412914854315</v>
+        <v>121.4372822768092</v>
       </c>
       <c r="D4" t="n">
-        <v>126.1467260140812</v>
+        <v>123.3899784605561</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.11635461738242</v>
+        <v>49.70097752749479</v>
       </c>
       <c r="C5" t="n">
-        <v>112.8028112179585</v>
+        <v>155.2143120414208</v>
       </c>
       <c r="D5" t="n">
-        <v>88.99542938997337</v>
+        <v>81.23962252642357</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.28561613314037</v>
+        <v>45.96739100824416</v>
       </c>
       <c r="C6" t="n">
-        <v>133.7965041255723</v>
+        <v>131.4619080848734</v>
       </c>
       <c r="D6" t="n">
-        <v>41.70071548558752</v>
+        <v>39.44662275663685</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.21793229480956</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="C7" t="n">
-        <v>140.3742137440259</v>
+        <v>98.15415372289186</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>11.18210635137117</v>
       </c>
       <c r="C8" t="n">
-        <v>103.9768993567797</v>
+        <v>65.08987279156352</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>50.36562072326985</v>
+        <v>37.49687181600267</v>
       </c>
       <c r="D9" t="n">
-        <v>28.06718511671205</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
         <v>28.20561154301086</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.813909904549611</v>
+        <v>7.364089529555324</v>
       </c>
       <c r="C2" t="n">
-        <v>7.395505456091222</v>
+        <v>10.23079282595601</v>
       </c>
       <c r="D2" t="n">
-        <v>10.7884255219682</v>
+        <v>15.70305452942773</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.27371198750239</v>
+        <v>28.84374755077129</v>
       </c>
       <c r="C3" t="n">
-        <v>27.1011453757332</v>
+        <v>28.55904071653972</v>
       </c>
       <c r="D3" t="n">
-        <v>71.6872173641021</v>
+        <v>73.9354196068273</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.97131799906114</v>
+        <v>57.4194779782832</v>
       </c>
       <c r="C4" t="n">
-        <v>95.28646867878692</v>
+        <v>113.3329549782518</v>
       </c>
       <c r="D4" t="n">
-        <v>135.0423419622615</v>
+        <v>134.3786805141907</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.74944301790137</v>
+        <v>59.81297888123694</v>
       </c>
       <c r="C5" t="n">
-        <v>143.8996697499763</v>
+        <v>190.3117924682442</v>
       </c>
       <c r="D5" t="n">
-        <v>109.8575681052181</v>
+        <v>102.7153535568226</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.44411948188061</v>
+        <v>55.99005332089985</v>
       </c>
       <c r="C6" t="n">
-        <v>155.0896300829814</v>
+        <v>184.5538421828367</v>
       </c>
       <c r="D6" t="n">
-        <v>56.15105994439633</v>
+        <v>52.40765594810324</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.79978988825843</v>
+        <v>36.23139902522853</v>
       </c>
       <c r="C7" t="n">
-        <v>166.9638685658466</v>
+        <v>141.0329664535755</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.49468733641593</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.60487975900305</v>
+        <v>16.94005663677871</v>
       </c>
       <c r="C8" t="n">
-        <v>141.6956461539421</v>
+        <v>94.46376410262809</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>83.53593040665682</v>
+        <v>56.02343274284421</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>43.98720588877834</v>
+        <v>37.15424186722054</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
         <v>30.03068052520567</v>
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>14.87936820556466</v>
+      </c>
+      <c r="D16" t="n">
         <v>14.46605242207675</v>
-      </c>
-      <c r="D16" t="n">
-        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2579,7 +2579,7 @@
         <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.447897937314798</v>
+        <v>4.433572632378596</v>
       </c>
       <c r="C2" t="n">
-        <v>3.445934441906304</v>
+        <v>4.857687640613218</v>
       </c>
       <c r="D2" t="n">
-        <v>7.547676350249478</v>
+        <v>10.96121311791564</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.52896639060656</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="C3" t="n">
-        <v>29.5947845445201</v>
+        <v>34.87167845484671</v>
       </c>
       <c r="D3" t="n">
-        <v>68.23146544515332</v>
+        <v>72.75241362320989</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.08916878129977</v>
+        <v>63.2520410892135</v>
       </c>
       <c r="C4" t="n">
-        <v>94.3420273873015</v>
+        <v>110.1805630999153</v>
       </c>
       <c r="D4" t="n">
-        <v>142.3936687716616</v>
+        <v>142.2532788499543</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.15472489330606</v>
+        <v>61.62921213409354</v>
       </c>
       <c r="C5" t="n">
-        <v>173.1802950291374</v>
+        <v>224.1084571869407</v>
       </c>
       <c r="D5" t="n">
-        <v>115.5762484824558</v>
+        <v>108.5076650118787</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.19882142453915</v>
+        <v>44.71958967614647</v>
       </c>
       <c r="C6" t="n">
-        <v>193.1676965398982</v>
+        <v>215.6281205176567</v>
       </c>
       <c r="D6" t="n">
-        <v>54.78250364467628</v>
+        <v>51.36111289537615</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.30049691295753</v>
+        <v>11.19879606234337</v>
       </c>
       <c r="C7" t="n">
-        <v>180.0191495369206</v>
+        <v>138.3979556153771</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>104.5610392408065</v>
+        <v>69.9298889735003</v>
       </c>
       <c r="D8" t="n">
-        <v>31.12631096314512</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>33.50312215512664</v>
+        <v>28.28906009787183</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
         <v>23.48831382410494</v>
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>22.92282714645877</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>12.541826921753</v>
+      </c>
+      <c r="D15" t="n">
         <v>12.18348900970292</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2876,7 +2876,7 @@
         <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.515057691831081</v>
+        <v>5.403539364174444</v>
       </c>
       <c r="C2" t="n">
-        <v>2.899100970640831</v>
+        <v>5.098215828153687</v>
       </c>
       <c r="D2" t="n">
-        <v>9.242172887779473</v>
+        <v>11.41478055727766</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.39795197758523</v>
+        <v>22.48693116577319</v>
       </c>
       <c r="C3" t="n">
-        <v>21.3775562599743</v>
+        <v>26.92443078896877</v>
       </c>
       <c r="D3" t="n">
-        <v>59.49881961587794</v>
+        <v>66.12070788102268</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.0471335564664</v>
+        <v>60.61015801708533</v>
       </c>
       <c r="C4" t="n">
-        <v>84.19566486391069</v>
+        <v>98.88555576255573</v>
       </c>
       <c r="D4" t="n">
-        <v>145.1376536050315</v>
+        <v>145.1248908848763</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.37748381117885</v>
+        <v>75.54548584179207</v>
       </c>
       <c r="C5" t="n">
-        <v>174.9474408967816</v>
+        <v>216.1808444751477</v>
       </c>
       <c r="D5" t="n">
-        <v>134.8430471782994</v>
+        <v>128.9771046454247</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.10702016642546</v>
+        <v>59.49194738194822</v>
       </c>
       <c r="C6" t="n">
-        <v>231.6482795555562</v>
+        <v>278.501206993031</v>
       </c>
       <c r="D6" t="n">
-        <v>72.17121898229578</v>
+        <v>67.70328518026855</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.55917958525995</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="C7" t="n">
-        <v>226.6109320850658</v>
+        <v>212.5375787446877</v>
       </c>
       <c r="D7" t="n">
-        <v>40.90255460203486</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.508987279156353</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>159.5536368941916</v>
+        <v>114.574865824124</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>68.55936917837174</v>
+        <v>49.36718330805084</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.058144098728814</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C2" t="n">
-        <v>1.944842202112931</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="D2" t="n">
-        <v>6.971390447856601</v>
+        <v>8.883834975729387</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.29348581030757</v>
+        <v>20.95049600862693</v>
       </c>
       <c r="C3" t="n">
-        <v>17.11677122354314</v>
+        <v>24.21971586376881</v>
       </c>
       <c r="D3" t="n">
-        <v>54.6637121724624</v>
+        <v>62.07099860100459</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.4015034199705</v>
+        <v>54.71378130537899</v>
       </c>
       <c r="C4" t="n">
-        <v>72.51777592189489</v>
+        <v>87.34805674224721</v>
       </c>
       <c r="D4" t="n">
-        <v>143.4019236639231</v>
+        <v>145.4439588887565</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.00428081484482</v>
+        <v>83.25220532012953</v>
       </c>
       <c r="C5" t="n">
-        <v>173.2539261069559</v>
+        <v>210.7321447165779</v>
       </c>
       <c r="D5" t="n">
-        <v>149.9374181310941</v>
+        <v>142.132523882332</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.88188114698346</v>
+        <v>70.03788122096746</v>
       </c>
       <c r="C6" t="n">
-        <v>258.3753790559714</v>
+        <v>312.9163727654029</v>
       </c>
       <c r="D6" t="n">
-        <v>85.5750203883775</v>
+        <v>81.26809320984674</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.12190094624263</v>
+        <v>21.4992929753009</v>
       </c>
       <c r="C7" t="n">
-        <v>270.9270234547668</v>
+        <v>274.460333442351</v>
       </c>
       <c r="D7" t="n">
-        <v>46.65166915810418</v>
+        <v>44.31609136970101</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>200.0261860017664</v>
+        <v>153.1280981698962</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>34.71459882216722</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>80.09686819868024</v>
+        <v>57.02187015806322</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.102723656047421</v>
+        <v>5.386849653202249</v>
       </c>
       <c r="C2" t="n">
-        <v>3.026728172192916</v>
+        <v>9.482701075319941</v>
       </c>
       <c r="D2" t="n">
-        <v>9.109636947706154</v>
+        <v>12.10298569795468</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.95554361586841</v>
+        <v>17.21985473248905</v>
       </c>
       <c r="C3" t="n">
-        <v>12.53691818323177</v>
+        <v>18.40286071610646</v>
       </c>
       <c r="D3" t="n">
-        <v>48.78795216254525</v>
+        <v>56.57321145722244</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.74761839121312</v>
+        <v>47.46455625722054</v>
       </c>
       <c r="C4" t="n">
-        <v>58.89995351628739</v>
+        <v>75.46596427774806</v>
       </c>
       <c r="D4" t="n">
-        <v>138.8583952886689</v>
+        <v>141.7682954840564</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.44606728175589</v>
+        <v>83.42401116837273</v>
       </c>
       <c r="C5" t="n">
-        <v>155.680642200938</v>
+        <v>189.5018506122406</v>
       </c>
       <c r="D5" t="n">
-        <v>162.2828955119978</v>
+        <v>156.2942345160922</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>69.43410638285567</v>
+        <v>85.05174886201394</v>
       </c>
       <c r="C6" t="n">
-        <v>268.8005579273682</v>
+        <v>322.5767701751915</v>
       </c>
       <c r="D6" t="n">
-        <v>103.648013875857</v>
+        <v>99.13982841795567</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.00992495469625</v>
+        <v>41.08221443191203</v>
       </c>
       <c r="C7" t="n">
-        <v>313.0273102559827</v>
+        <v>343.62936794506</v>
       </c>
       <c r="D7" t="n">
-        <v>56.41318658143022</v>
+        <v>52.81998998388688</v>
       </c>
     </row>
     <row r="8">
@@ -3663,10 +3663,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
-        <v>262.5291535926395</v>
+        <v>233.1552622815749</v>
       </c>
       <c r="D8" t="n">
         <v>37.21805546799658</v>
@@ -3680,10 +3680,10 @@
         <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>142.6656128857379</v>
+        <v>103.5046787110369</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>53.80959166976768</v>
+        <v>42.56367171762047</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3739,7 +3739,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3781,7 +3781,7 @@
         <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.949211161286423</v>
+        <v>8.031677968443155</v>
       </c>
       <c r="C2" t="n">
-        <v>8.638398049667684</v>
+        <v>3.223077713042279</v>
       </c>
       <c r="D2" t="n">
-        <v>15.56266460772044</v>
+        <v>3.181844309463912</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.938370878810703</v>
+        <v>3.899501881268331</v>
       </c>
       <c r="C2" t="n">
-        <v>1.719040230136165</v>
+        <v>5.538038799656257</v>
       </c>
       <c r="D2" t="n">
-        <v>6.705336820005715</v>
+        <v>9.004589943351744</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.39304323906399</v>
+        <v>22.88944772451438</v>
       </c>
       <c r="C3" t="n">
-        <v>14.22061549601505</v>
+        <v>26.31574721233575</v>
       </c>
       <c r="D3" t="n">
-        <v>53.33835277172921</v>
+        <v>61.35923151542565</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.22505087511333</v>
+        <v>63.94122797759476</v>
       </c>
       <c r="C4" t="n">
-        <v>84.84656359182634</v>
+        <v>108.7383757223767</v>
       </c>
       <c r="D4" t="n">
-        <v>143.4146863840783</v>
+        <v>146.0693321763617</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.98796665230434</v>
+        <v>49.45554060143309</v>
       </c>
       <c r="C5" t="n">
-        <v>230.1216618754524</v>
+        <v>276.190172897234</v>
       </c>
       <c r="D5" t="n">
-        <v>149.3483695085461</v>
+        <v>142.7215725048801</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.98369550412208</v>
+        <v>25.47929816831747</v>
       </c>
       <c r="C6" t="n">
-        <v>258.8583989264608</v>
+        <v>286.3905315443583</v>
       </c>
       <c r="D6" t="n">
-        <v>83.07941772418209</v>
+        <v>77.8467024605466</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.767186925373263</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>184.6304185037679</v>
+        <v>163.9695380678938</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>105.1451791248334</v>
+        <v>76.2719791429347</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>24.36697801940583</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>41.04687151455913</v>
+        <v>32.50468473990763</v>
       </c>
       <c r="D9" t="n">
-        <v>19.96874830438012</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
         <v>16.17036643664921</v>
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4389,7 +4389,7 @@
         <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.701810739816227</v>
+        <v>7.942338927356696</v>
       </c>
       <c r="C2" t="n">
-        <v>7.316965639751478</v>
+        <v>5.667629496616836</v>
       </c>
       <c r="D2" t="n">
-        <v>20.32512272102171</v>
+        <v>25.33203601268045</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.87624303600267</v>
+        <v>17.0529576227671</v>
       </c>
       <c r="C3" t="n">
-        <v>21.76534660315179</v>
+        <v>8.246680715673207</v>
       </c>
       <c r="D3" t="n">
-        <v>16.20865459711484</v>
+        <v>5.934664872171969</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39648557404594</v>
+        <v>13.39952630405068</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13454212294641</v>
+        <v>70.15046123885357</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576057126358346</v>
+        <v>1.57641485930008</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.393721887131976</v>
+        <v>6.042657119639118</v>
       </c>
       <c r="C2" t="n">
-        <v>9.364891350810323</v>
+        <v>4.467933802027233</v>
       </c>
       <c r="D2" t="n">
-        <v>22.16295442337174</v>
+        <v>25.90537667196059</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.75691178444107</v>
+        <v>23.32141671438298</v>
       </c>
       <c r="C3" t="n">
-        <v>26.00158794697677</v>
+        <v>16.91551294417254</v>
       </c>
       <c r="D3" t="n">
-        <v>29.3640738340221</v>
+        <v>25.77578597500001</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.50143639715864</v>
+        <v>19.69287719948677</v>
       </c>
       <c r="C4" t="n">
-        <v>33.71910665006095</v>
+        <v>13.12007631955437</v>
       </c>
       <c r="D4" t="n">
-        <v>23.55998140651495</v>
+        <v>18.17411350101695</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.60312155223957</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
@@ -4991,10 +4991,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
         <v>44.86390658867074</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43550097857097</v>
+        <v>15.44263752044844</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1138475646591</v>
+        <v>86.15366195618603</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249579153383362</v>
+        <v>3.251081583252303</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.980807014271569</v>
+        <v>5.936628367580462</v>
       </c>
       <c r="C2" t="n">
-        <v>6.304783756673016</v>
+        <v>4.862596379134452</v>
       </c>
       <c r="D2" t="n">
-        <v>24.42097414313941</v>
+        <v>20.29272504678157</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.43507846389736</v>
+        <v>21.97642235956485</v>
       </c>
       <c r="C3" t="n">
-        <v>32.20623343781661</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D3" t="n">
-        <v>40.28110830524663</v>
+        <v>40.51672775426587</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.99163160121406</v>
+        <v>34.03817465394117</v>
       </c>
       <c r="C4" t="n">
-        <v>51.8804574309227</v>
+        <v>30.32422308877548</v>
       </c>
       <c r="D4" t="n">
-        <v>32.96610616090365</v>
+        <v>26.99315312826605</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.56699250916493</v>
+        <v>16.98423528346982</v>
       </c>
       <c r="C5" t="n">
-        <v>37.23278168356029</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D5" t="n">
-        <v>31.39138284329177</v>
+        <v>28.98610096788708</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.3572583533546</v>
+        <v>12.07549676223577</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.49062147687869</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9695754878309</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5302,10 +5302,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72176227104086</v>
+        <v>16.73668130498685</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0027498533492</v>
+        <v>102.0937559604198</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180440567760215</v>
+        <v>5.021004391496053</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.639158813193679</v>
+        <v>8.444993751931063</v>
       </c>
       <c r="C2" t="n">
-        <v>4.628940425523711</v>
+        <v>8.69239417340126</v>
       </c>
       <c r="D2" t="n">
-        <v>24.28941995077033</v>
+        <v>18.8083225179604</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.40562603276996</v>
+        <v>21.08303194870025</v>
       </c>
       <c r="C3" t="n">
-        <v>27.78346003018473</v>
+        <v>18.15742379004476</v>
       </c>
       <c r="D3" t="n">
-        <v>49.8776921142592</v>
+        <v>46.92754026299754</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.55243052451725</v>
+        <v>38.82419471214436</v>
       </c>
       <c r="C4" t="n">
-        <v>67.61689138229482</v>
+        <v>37.13951565165684</v>
       </c>
       <c r="D4" t="n">
-        <v>45.05240214788613</v>
+        <v>40.20256848890688</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.49584901056943</v>
+        <v>33.87029579651497</v>
       </c>
       <c r="C5" t="n">
-        <v>67.91239744127311</v>
+        <v>38.04272353956391</v>
       </c>
       <c r="D5" t="n">
-        <v>35.66198535676539</v>
+        <v>32.2749557771139</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.00757624419349</v>
+        <v>14.4503444588088</v>
       </c>
       <c r="C6" t="n">
-        <v>36.50825187782615</v>
+        <v>19.24029150782899</v>
       </c>
       <c r="D6" t="n">
-        <v>38.23907308041327</v>
+        <v>37.99756314516856</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>42.3781214015178</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>48.54251523648354</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
         <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03609024224323</v>
+        <v>18.06525706963169</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6640172946344</v>
+        <v>117.8542961209306</v>
       </c>
       <c r="D21" t="n">
-        <v>6.012030080747745</v>
+        <v>6.882002693193026</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.660176425610362</v>
+        <v>9.922524046822513</v>
       </c>
       <c r="C2" t="n">
-        <v>4.0938879267092</v>
+        <v>14.2343599638745</v>
       </c>
       <c r="D2" t="n">
-        <v>28.3783991389583</v>
+        <v>22.4535517438288</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5291052593268</v>
+        <v>23.04161861867264</v>
       </c>
       <c r="C3" t="n">
-        <v>20.87195619228719</v>
+        <v>25.46653544816226</v>
       </c>
       <c r="D3" t="n">
-        <v>53.85377031645879</v>
+        <v>47.78166076569227</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.46537377400877</v>
+        <v>28.88203571123692</v>
       </c>
       <c r="C4" t="n">
-        <v>57.35566437750716</v>
+        <v>34.68907338185679</v>
       </c>
       <c r="D4" t="n">
-        <v>51.57415214719769</v>
+        <v>46.69879304790803</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.80171232593793</v>
+        <v>28.29887757491431</v>
       </c>
       <c r="C5" t="n">
-        <v>72.18299995474675</v>
+        <v>40.71798603363646</v>
       </c>
       <c r="D5" t="n">
-        <v>35.12202411942965</v>
+        <v>32.0295188510522</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.53713916741002</v>
+        <v>16.66418553188536</v>
       </c>
       <c r="C6" t="n">
-        <v>49.46928506929254</v>
+        <v>27.45162930614931</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>30.83276839957533</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.228207435741766</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>23.53543771390878</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>30.66194429903638</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5955,7 +5955,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
         <v>26.03889435973815</v>
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.044268132665879</v>
+        <v>7.062171855391171</v>
       </c>
       <c r="C21" t="n">
-        <v>66.04001374374262</v>
+        <v>66.20786114429222</v>
       </c>
       <c r="D21" t="n">
-        <v>4.402667582916174</v>
+        <v>5.296628891543378</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.717698629533423</v>
+        <v>8.309512568745003</v>
       </c>
       <c r="C2" t="n">
-        <v>6.005350706877739</v>
+        <v>8.462665210607506</v>
       </c>
       <c r="D2" t="n">
-        <v>27.14041528390307</v>
+        <v>20.76690918793278</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.01921834792421</v>
+        <v>30.26237298340793</v>
       </c>
       <c r="C3" t="n">
-        <v>17.76472470834603</v>
+        <v>45.23893421169302</v>
       </c>
       <c r="D3" t="n">
-        <v>64.67753875577988</v>
+        <v>55.53746762924207</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.88127494771092</v>
+        <v>39.10497455555895</v>
       </c>
       <c r="C4" t="n">
-        <v>54.31813698056752</v>
+        <v>53.33540752861647</v>
       </c>
       <c r="D4" t="n">
-        <v>67.83385762493337</v>
+        <v>61.64393834965723</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.12202411942965</v>
+        <v>37.20823799095412</v>
       </c>
       <c r="C5" t="n">
-        <v>92.62789589568656</v>
+        <v>55.32148313430778</v>
       </c>
       <c r="D5" t="n">
-        <v>45.99487994396307</v>
+        <v>42.68148144213009</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.49188096202344</v>
+        <v>29.42396044398116</v>
       </c>
       <c r="C6" t="n">
-        <v>86.74231840872694</v>
+        <v>49.75104666041137</v>
       </c>
       <c r="D6" t="n">
-        <v>35.86422538384024</v>
+        <v>34.25415914887547</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.1750541909922</v>
+        <v>14.13323995033708</v>
       </c>
       <c r="C7" t="n">
-        <v>51.44259795482861</v>
+        <v>30.00319158948677</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>26.20284622634736</v>
+        <v>20.5283444958008</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6193,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
         <v>23.10052348092744</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.261498152136733</v>
+        <v>7.286217852936552</v>
       </c>
       <c r="C21" t="n">
-        <v>75.33804332841861</v>
+        <v>75.59451022421673</v>
       </c>
       <c r="D21" t="n">
-        <v>5.446123614102549</v>
+        <v>6.375440621319483</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.830198704894307</v>
+        <v>6.407867265618932</v>
       </c>
       <c r="C2" t="n">
-        <v>4.60439673291754</v>
+        <v>5.862997289761952</v>
       </c>
       <c r="D2" t="n">
-        <v>23.62870374581223</v>
+        <v>31.59165937495811</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.28781630826034</v>
+        <v>29.43279617331937</v>
       </c>
       <c r="C3" t="n">
-        <v>21.09284942574272</v>
+        <v>37.77765165941727</v>
       </c>
       <c r="D3" t="n">
-        <v>71.38287557578558</v>
+        <v>59.26320016685872</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.01188845010475</v>
+        <v>50.17025293012475</v>
       </c>
       <c r="C4" t="n">
-        <v>48.65148923165493</v>
+        <v>88.63709147792328</v>
       </c>
       <c r="D4" t="n">
-        <v>85.02524167399926</v>
+        <v>75.6574050800762</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.87153958612647</v>
+        <v>49.30827844579606</v>
       </c>
       <c r="C5" t="n">
-        <v>97.04576056479723</v>
+        <v>79.47247665877931</v>
       </c>
       <c r="D5" t="n">
-        <v>59.98478472948013</v>
+        <v>54.8060655895782</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.15856976866503</v>
+        <v>40.85543071223103</v>
       </c>
       <c r="C6" t="n">
-        <v>119.5474179461341</v>
+        <v>71.16492758544281</v>
       </c>
       <c r="D6" t="n">
-        <v>41.82147045320988</v>
+        <v>40.29190752999335</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.65521093382689</v>
+        <v>25.63146906247572</v>
       </c>
       <c r="C7" t="n">
-        <v>90.4287810381737</v>
+        <v>53.23919625360028</v>
       </c>
       <c r="D7" t="n">
-        <v>36.83026512481909</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>48.90085314853362</v>
+        <v>31.29320807286708</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>28.73281006019139</v>
+        <v>25.07187287105504</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +6619,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.465706206314437</v>
+        <v>7.496741852939254</v>
       </c>
       <c r="C21" t="n">
-        <v>83.98919482103742</v>
+        <v>85.275438577184</v>
       </c>
       <c r="D21" t="n">
-        <v>6.532492930525132</v>
+        <v>7.496741852939254</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_63_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_63_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497624594625</v>
+        <v>10.84497650750534</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907164130779</v>
+        <v>37.78907255270448</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.430267536367362</v>
+        <v>1.282162501746335</v>
       </c>
       <c r="C2" t="n">
-        <v>6.034803138005143</v>
+        <v>2.357176237896592</v>
       </c>
       <c r="D2" t="n">
-        <v>36.0252320073367</v>
+        <v>13.20254312671111</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.32418203104648</v>
+        <v>10.47033926579223</v>
       </c>
       <c r="C3" t="n">
-        <v>29.34443887993716</v>
+        <v>31.74972075534185</v>
       </c>
       <c r="D3" t="n">
-        <v>69.39483647468579</v>
+        <v>52.75912162622359</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.27159392784043</v>
+        <v>16.25970547773567</v>
       </c>
       <c r="C4" t="n">
-        <v>90.9088556655504</v>
+        <v>113.7541247433737</v>
       </c>
       <c r="D4" t="n">
-        <v>86.17388648796803</v>
+        <v>60.21451369227387</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.58641614573418</v>
+        <v>12.41910845872215</v>
       </c>
       <c r="C5" t="n">
-        <v>124.0929098167969</v>
+        <v>134.7694161004809</v>
       </c>
       <c r="D5" t="n">
-        <v>68.79597037509525</v>
+        <v>44.03138453546945</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.61520562432682</v>
+        <v>8.774860980557992</v>
       </c>
       <c r="C6" t="n">
-        <v>99.34108669732626</v>
+        <v>88.23162967606936</v>
       </c>
       <c r="D6" t="n">
-        <v>47.41645061971246</v>
+        <v>29.3032054763588</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.42913122440964</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>77.97236616669016</v>
+        <v>42.04040019125691</v>
       </c>
       <c r="D7" t="n">
-        <v>39.34550274309942</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.19316761802514</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>51.40430979436299</v>
+        <v>28.45595720759379</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.653124265231384</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>32.50468473990763</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.83437204208531</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.691238419923476</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.21767064406257</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.652643222413911</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.425759708473628</v>
+        <v>1.788744317137688</v>
       </c>
       <c r="C2" t="n">
-        <v>10.31915011933822</v>
+        <v>6.351907646476863</v>
       </c>
       <c r="D2" t="n">
-        <v>26.96860943565988</v>
+        <v>10.47426625660922</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.55136666135499</v>
+        <v>7.274750488468865</v>
       </c>
       <c r="C3" t="n">
-        <v>26.1930287493049</v>
+        <v>18.57466656434965</v>
       </c>
       <c r="D3" t="n">
-        <v>79.78663592413828</v>
+        <v>51.58593311964866</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.22130381074558</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="C4" t="n">
-        <v>81.26023922821274</v>
+        <v>94.30373922683586</v>
       </c>
       <c r="D4" t="n">
-        <v>98.92384392302137</v>
+        <v>72.41567416065323</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>70.75946578358887</v>
+        <v>18.60411899547706</v>
       </c>
       <c r="C5" t="n">
-        <v>144.8814174542231</v>
+        <v>177.598159698248</v>
       </c>
       <c r="D5" t="n">
-        <v>80.92055452254336</v>
+        <v>55.07604620824608</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.22026530977911</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="C6" t="n">
-        <v>143.3763982236127</v>
+        <v>154.4053519331214</v>
       </c>
       <c r="D6" t="n">
-        <v>56.79508643838223</v>
+        <v>35.90447703971436</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.34656660626167</v>
+        <v>8.024805734513427</v>
       </c>
       <c r="C7" t="n">
-        <v>108.6941970756856</v>
+        <v>85.27853258169493</v>
       </c>
       <c r="D7" t="n">
-        <v>43.11835917051991</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.87319998189869</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>74.93680226515903</v>
+        <v>42.22496875965531</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.53437385074652</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>47.14843349645305</v>
+        <v>34.83437204208531</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.869033539789666</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102.2974360172657</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.836291924737083</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.6356737907332</v>
+        <v>0.9464047868939253</v>
       </c>
       <c r="C2" t="n">
-        <v>12.44757914214531</v>
+        <v>2.622248118043231</v>
       </c>
       <c r="D2" t="n">
-        <v>20.90239037111884</v>
+        <v>7.053857255013333</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.20070280448963</v>
+        <v>7.451465075233291</v>
       </c>
       <c r="C3" t="n">
-        <v>32.40258297866598</v>
+        <v>22.96798754085413</v>
       </c>
       <c r="D3" t="n">
-        <v>81.28380117311467</v>
+        <v>50.28020867300039</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.13647259755286</v>
+        <v>20.08852152429823</v>
       </c>
       <c r="C4" t="n">
-        <v>73.88338697850222</v>
+        <v>84.1829021437555</v>
       </c>
       <c r="D4" t="n">
-        <v>110.588970144882</v>
+        <v>81.4899681910065</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>72.10936887692823</v>
+        <v>18.21141991377834</v>
       </c>
       <c r="C5" t="n">
-        <v>145.1759417654971</v>
+        <v>198.779366417373</v>
       </c>
       <c r="D5" t="n">
-        <v>94.19869222248147</v>
+        <v>61.48194997845651</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>78.49072895453251</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C6" t="n">
-        <v>178.6771004252153</v>
+        <v>200.0104780384985</v>
       </c>
       <c r="D6" t="n">
-        <v>65.69070238656259</v>
+        <v>36.74976181307086</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>61.92275469766331</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>150.6747106569835</v>
+        <v>80.00851090529807</v>
       </c>
       <c r="D7" t="n">
-        <v>48.32849423695774</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>39.30426933952106</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>103.3927594727528</v>
+        <v>40.55599766243574</v>
       </c>
       <c r="D8" t="n">
-        <v>40.3056519978528</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.74687332322034</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>66.11874438561416</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.252972112526189</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>43.2754388031994</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.18387422479719</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.030614307722326</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110.420946731182</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0420946731182</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.57145927932965</v>
+        <v>0.7775441817634738</v>
       </c>
       <c r="C2" t="n">
-        <v>8.563785224144926</v>
+        <v>6.284167054883833</v>
       </c>
       <c r="D2" t="n">
-        <v>17.50161632360789</v>
+        <v>7.329728359906686</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>33.88011327355743</v>
+        <v>5.296528864411542</v>
       </c>
       <c r="C3" t="n">
-        <v>49.80406103644069</v>
+        <v>15.79141182280995</v>
       </c>
       <c r="D3" t="n">
-        <v>87.19392235268047</v>
+        <v>44.93950116189774</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.63802250123597</v>
+        <v>17.52321477310132</v>
       </c>
       <c r="C4" t="n">
-        <v>112.8990224929747</v>
+        <v>70.30982533504381</v>
       </c>
       <c r="D4" t="n">
-        <v>106.0454417696277</v>
+        <v>87.51397210426492</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.20319038371264</v>
+        <v>23.93010029101601</v>
       </c>
       <c r="C5" t="n">
-        <v>106.7650628368407</v>
+        <v>178.1135772429776</v>
       </c>
       <c r="D5" t="n">
-        <v>64.57445524683396</v>
+        <v>75.15278676009335</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.44033135978387</v>
+        <v>16.70443718775948</v>
       </c>
       <c r="C6" t="n">
-        <v>99.22033172970391</v>
+        <v>259.1804121734538</v>
       </c>
       <c r="D6" t="n">
-        <v>31.79880814055419</v>
+        <v>46.4504108787336</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.05067533218911</v>
+        <v>7.485826244881928</v>
       </c>
       <c r="C7" t="n">
-        <v>72.7023444902933</v>
+        <v>179.5999432672072</v>
       </c>
       <c r="D7" t="n">
-        <v>28.32636651063322</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.68556299720053</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>48.73395603881166</v>
+        <v>70.84782307697107</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>32.9484347022272</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>27.61656292046278</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>47.6942852200143</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.409830761027425</v>
+        <v>0.4368777283898306</v>
       </c>
       <c r="C2" t="n">
-        <v>4.241150082346221</v>
+        <v>3.765002445786517</v>
       </c>
       <c r="D2" t="n">
-        <v>12.39751000922872</v>
+        <v>5.097234080449439</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>35.96141840656067</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C3" t="n">
-        <v>42.32805226860123</v>
+        <v>20.700150344044</v>
       </c>
       <c r="D3" t="n">
-        <v>82.2115527536279</v>
+        <v>41.21867736280234</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.64323433939346</v>
+        <v>14.99619618237003</v>
       </c>
       <c r="C4" t="n">
-        <v>121.4372822768092</v>
+        <v>56.71752836974673</v>
       </c>
       <c r="D4" t="n">
-        <v>123.3899784605561</v>
+        <v>91.03648286710248</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.70097752749479</v>
+        <v>26.08994524035899</v>
       </c>
       <c r="C5" t="n">
-        <v>155.2143120414208</v>
+        <v>164.8354395430395</v>
       </c>
       <c r="D5" t="n">
-        <v>81.23962252642357</v>
+        <v>85.19115703601699</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.96739100824416</v>
+        <v>21.01136436629024</v>
       </c>
       <c r="C6" t="n">
-        <v>131.4619080848734</v>
+        <v>281.5200811835899</v>
       </c>
       <c r="D6" t="n">
-        <v>39.44662275663685</v>
+        <v>55.34602682691394</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.49362347325367</v>
+        <v>8.444012004226815</v>
       </c>
       <c r="C7" t="n">
-        <v>98.15415372289186</v>
+        <v>252.3621743674596</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>39.1059563032632</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>65.08987279156352</v>
+        <v>114.658314378985</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>37.49687181600267</v>
+        <v>48.8124958551514</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.364089529555324</v>
+        <v>0.5988660995905544</v>
       </c>
       <c r="C2" t="n">
-        <v>10.23079282595601</v>
+        <v>11.90467266169682</v>
       </c>
       <c r="D2" t="n">
-        <v>15.70305452942773</v>
+        <v>8.600109889202058</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.84374755077129</v>
+        <v>2.827433388230814</v>
       </c>
       <c r="C3" t="n">
-        <v>28.55904071653972</v>
+        <v>17.61255381418778</v>
       </c>
       <c r="D3" t="n">
-        <v>73.9354196068273</v>
+        <v>36.30503010304705</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>57.4194779782832</v>
+        <v>11.70341438232623</v>
       </c>
       <c r="C4" t="n">
-        <v>113.3329549782518</v>
+        <v>54.1394588983946</v>
       </c>
       <c r="D4" t="n">
-        <v>134.3786805141907</v>
+        <v>90.89609294539518</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.81297888123694</v>
+        <v>24.7645858396258</v>
       </c>
       <c r="C5" t="n">
-        <v>190.3117924682442</v>
+        <v>135.7020764195154</v>
       </c>
       <c r="D5" t="n">
-        <v>102.7153535568226</v>
+        <v>96.38308086443064</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.99005332089985</v>
+        <v>27.2101193709046</v>
       </c>
       <c r="C6" t="n">
-        <v>184.5538421828367</v>
+        <v>276.6093791669473</v>
       </c>
       <c r="D6" t="n">
-        <v>52.40765594810324</v>
+        <v>66.73724543928969</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.23139902522853</v>
+        <v>15.03153909972291</v>
       </c>
       <c r="C7" t="n">
-        <v>141.0329664535755</v>
+        <v>322.3696214095954</v>
       </c>
       <c r="D7" t="n">
-        <v>34.49468733641593</v>
+        <v>44.6155244194963</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.94005663677871</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>94.46376410262809</v>
+        <v>210.9579466885546</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>41.55738032076748</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>56.02343274284421</v>
+        <v>87.75155504869262</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>42.48905889209769</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>37.15424186722054</v>
+        <v>43.41779222031519</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.433572632378596</v>
+        <v>0.4015348110369454</v>
       </c>
       <c r="C2" t="n">
-        <v>4.857687640613218</v>
+        <v>6.189919275276139</v>
       </c>
       <c r="D2" t="n">
-        <v>10.96121311791564</v>
+        <v>6.191882770684633</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.6242369756475</v>
+        <v>4.054618018539327</v>
       </c>
       <c r="C3" t="n">
-        <v>34.87167845484671</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D3" t="n">
-        <v>72.75241362320989</v>
+        <v>39.96694903988765</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>63.2520410892135</v>
+        <v>17.74018101573986</v>
       </c>
       <c r="C4" t="n">
-        <v>110.1805630999153</v>
+        <v>77.72496574521998</v>
       </c>
       <c r="D4" t="n">
-        <v>142.2532788499543</v>
+        <v>93.95914578264522</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.62921213409354</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="C5" t="n">
-        <v>224.1084571869407</v>
+        <v>219.0524565100696</v>
       </c>
       <c r="D5" t="n">
-        <v>108.5076650118787</v>
+        <v>90.3698761759189</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.71958967614647</v>
+        <v>9.298132506921544</v>
       </c>
       <c r="C6" t="n">
-        <v>215.6281205176567</v>
+        <v>280.0710215721216</v>
       </c>
       <c r="D6" t="n">
-        <v>51.36111289537615</v>
+        <v>58.96867585558468</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.19879606234337</v>
+        <v>4.012402867256713</v>
       </c>
       <c r="C7" t="n">
-        <v>138.3979556153771</v>
+        <v>148.3391328685803</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>35.75230614555609</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>69.9298889735003</v>
+        <v>64.67263001725863</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>28.28906009787183</v>
+        <v>33.05937219280708</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>26.95781021091316</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.403539364174444</v>
+        <v>0.2287472150895068</v>
       </c>
       <c r="C2" t="n">
-        <v>5.098215828153687</v>
+        <v>4.112541133089889</v>
       </c>
       <c r="D2" t="n">
-        <v>11.41478055727766</v>
+        <v>5.130613502393831</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.48693116577319</v>
+        <v>2.699806186678729</v>
       </c>
       <c r="C3" t="n">
-        <v>26.92443078896877</v>
+        <v>27.14041528390307</v>
       </c>
       <c r="D3" t="n">
-        <v>66.12070788102268</v>
+        <v>35.80433877388118</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>60.61015801708533</v>
+        <v>12.02248238620644</v>
       </c>
       <c r="C4" t="n">
-        <v>98.88555576255573</v>
+        <v>74.7767773893668</v>
       </c>
       <c r="D4" t="n">
-        <v>145.1248908848763</v>
+        <v>89.04549852288996</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>75.54548584179207</v>
+        <v>16.93514789825748</v>
       </c>
       <c r="C5" t="n">
-        <v>216.1808444751477</v>
+        <v>163.6818859905495</v>
       </c>
       <c r="D5" t="n">
-        <v>128.9771046454247</v>
+        <v>92.25974050659401</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.49194738194822</v>
+        <v>9.539642442166258</v>
       </c>
       <c r="C6" t="n">
-        <v>278.501206993031</v>
+        <v>261.313749934782</v>
       </c>
       <c r="D6" t="n">
-        <v>67.70328518026855</v>
+        <v>61.70578845502478</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.13430381349934</v>
+        <v>3.413536767666159</v>
       </c>
       <c r="C7" t="n">
-        <v>212.5375787446877</v>
+        <v>190.0801000100419</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.926230053461247</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>114.574865824124</v>
+        <v>77.02301613668349</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>49.36718330805084</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>21.63281066307846</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>18.50594422505238</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.902447124381071</v>
+        <v>0.3504839304161113</v>
       </c>
       <c r="C2" t="n">
-        <v>2.995312245657018</v>
+        <v>3.981968688425063</v>
       </c>
       <c r="D2" t="n">
-        <v>8.883834975729387</v>
+        <v>7.723409189309657</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.95049600862693</v>
+        <v>1.644427404613407</v>
       </c>
       <c r="C3" t="n">
-        <v>24.21971586376881</v>
+        <v>20.38599107868502</v>
       </c>
       <c r="D3" t="n">
-        <v>62.07099860100459</v>
+        <v>31.59754986118359</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>54.71378130537899</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="C4" t="n">
-        <v>87.34805674224721</v>
+        <v>71.54780919009904</v>
       </c>
       <c r="D4" t="n">
-        <v>145.4439588887565</v>
+        <v>87.10556505929826</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>83.25220532012953</v>
+        <v>17.76963344686727</v>
       </c>
       <c r="C5" t="n">
-        <v>210.7321447165779</v>
+        <v>149.5692627420016</v>
       </c>
       <c r="D5" t="n">
-        <v>142.132523882332</v>
+        <v>103.8443634167064</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>70.03788122096746</v>
+        <v>16.30192062901829</v>
       </c>
       <c r="C6" t="n">
-        <v>312.9163727654029</v>
+        <v>264.6143857164598</v>
       </c>
       <c r="D6" t="n">
-        <v>81.26809320984674</v>
+        <v>76.31713953733006</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.4992929753009</v>
+        <v>7.246279805045708</v>
       </c>
       <c r="C7" t="n">
-        <v>274.460333442351</v>
+        <v>291.1686976209275</v>
       </c>
       <c r="D7" t="n">
-        <v>44.31609136970101</v>
+        <v>42.99858595060179</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>153.1280981698962</v>
+        <v>166.062624173348</v>
       </c>
       <c r="D8" t="n">
-        <v>34.71459882216722</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>57.02187015806322</v>
+        <v>63.12343213995715</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>23.74062298409636</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>17.41424077792992</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.386849653202249</v>
+        <v>0.4624031687002477</v>
       </c>
       <c r="C2" t="n">
-        <v>9.482701075319941</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="D2" t="n">
-        <v>12.10298569795468</v>
+        <v>9.798823836087415</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.21985473248905</v>
+        <v>1.413716694115407</v>
       </c>
       <c r="C3" t="n">
-        <v>18.40286071610646</v>
+        <v>17.60273633714531</v>
       </c>
       <c r="D3" t="n">
-        <v>56.57321145722244</v>
+        <v>30.43417883165112</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.46455625722054</v>
+        <v>5.730461349688633</v>
       </c>
       <c r="C4" t="n">
-        <v>75.46596427774806</v>
+        <v>60.44424265506763</v>
       </c>
       <c r="D4" t="n">
-        <v>141.7682954840564</v>
+        <v>83.5958170166159</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>83.42401116837273</v>
+        <v>15.65887588273663</v>
       </c>
       <c r="C5" t="n">
-        <v>189.5018506122406</v>
+        <v>140.4635527851124</v>
       </c>
       <c r="D5" t="n">
-        <v>156.2942345160922</v>
+        <v>110.0784613386736</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.05174886201394</v>
+        <v>20.20633124880786</v>
       </c>
       <c r="C6" t="n">
-        <v>322.5767701751915</v>
+        <v>252.5791406100982</v>
       </c>
       <c r="D6" t="n">
-        <v>99.13982841795567</v>
+        <v>90.60647737264239</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.08221443191203</v>
+        <v>12.93550775115597</v>
       </c>
       <c r="C7" t="n">
-        <v>343.62936794506</v>
+        <v>339.257645418049</v>
       </c>
       <c r="D7" t="n">
-        <v>52.81998998388688</v>
+        <v>53.59851591335461</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>233.1552622815749</v>
+        <v>273.9616056085937</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>103.5046787110369</v>
+        <v>131.0171763748496</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>25.84843530511426</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>42.56367171762047</v>
+        <v>49.53898915629405</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.031677968443155</v>
+        <v>2.555489274154447</v>
       </c>
       <c r="C2" t="n">
-        <v>3.223077713042279</v>
+        <v>6.865361695797945</v>
       </c>
       <c r="D2" t="n">
-        <v>3.181844309463912</v>
+        <v>8.728718838458391</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.899501881268331</v>
+        <v>0.8109236037078654</v>
       </c>
       <c r="C2" t="n">
-        <v>5.538038799656257</v>
+        <v>20.5764501333089</v>
       </c>
       <c r="D2" t="n">
-        <v>9.004589943351744</v>
+        <v>16.16349420271948</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.88944772451438</v>
+        <v>1.457895340806513</v>
       </c>
       <c r="C3" t="n">
-        <v>26.31574721233575</v>
+        <v>27.09623663721197</v>
       </c>
       <c r="D3" t="n">
-        <v>61.35923151542565</v>
+        <v>30.81215169778614</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>63.94122797759476</v>
+        <v>4.224460371374025</v>
       </c>
       <c r="C4" t="n">
-        <v>108.7383757223767</v>
+        <v>51.84216927045707</v>
       </c>
       <c r="D4" t="n">
-        <v>146.0693321763617</v>
+        <v>79.56279744757001</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.45554060143309</v>
+        <v>12.76272015520854</v>
       </c>
       <c r="C5" t="n">
-        <v>276.190172897234</v>
+        <v>126.5963664626262</v>
       </c>
       <c r="D5" t="n">
-        <v>142.7215725048801</v>
+        <v>114.4963260077843</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.47929816831747</v>
+        <v>20.68935111929729</v>
       </c>
       <c r="C6" t="n">
-        <v>286.3905315443583</v>
+        <v>238.1287961512894</v>
       </c>
       <c r="D6" t="n">
-        <v>77.8467024605466</v>
+        <v>101.4341728027805</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.006733365209485</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="C7" t="n">
-        <v>163.9695380678938</v>
+        <v>354.8281640074034</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>64.97697180557515</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>76.2719791429347</v>
+        <v>355.657740817492</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>38.63668090063322</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>32.50468473990763</v>
+        <v>220.9874812351399</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>94.80737579911448</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>37.6716229073586</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.942338927356696</v>
+        <v>3.667809423066083</v>
       </c>
       <c r="C2" t="n">
-        <v>5.667629496616836</v>
+        <v>14.78315693054847</v>
       </c>
       <c r="D2" t="n">
-        <v>25.33203601268045</v>
+        <v>16.78984923802895</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.0529576227671</v>
+        <v>4.231332605303753</v>
       </c>
       <c r="C3" t="n">
-        <v>8.246680715673207</v>
+        <v>13.55302705712722</v>
       </c>
       <c r="D3" t="n">
-        <v>5.934664872171969</v>
+        <v>8.997717709422018</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39952630405068</v>
+        <v>11.67861468252675</v>
       </c>
       <c r="C21" t="n">
-        <v>70.15046123885357</v>
+        <v>59.95022203697064</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57641485930008</v>
+        <v>0.7785743121684499</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.042657119639118</v>
+        <v>1.990984344212531</v>
       </c>
       <c r="C2" t="n">
-        <v>4.467933802027233</v>
+        <v>6.400013283984956</v>
       </c>
       <c r="D2" t="n">
-        <v>25.90537667196059</v>
+        <v>15.97401689579985</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.32141671438298</v>
+        <v>9.576948854927634</v>
       </c>
       <c r="C3" t="n">
-        <v>16.91551294417254</v>
+        <v>42.98582323044659</v>
       </c>
       <c r="D3" t="n">
-        <v>25.77578597500001</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.69287719948677</v>
+        <v>5.436918786118836</v>
       </c>
       <c r="C4" t="n">
-        <v>13.12007631955437</v>
+        <v>22.59001467471911</v>
       </c>
       <c r="D4" t="n">
-        <v>18.17411350101695</v>
+        <v>18.92711399017426</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44263752044844</v>
+        <v>13.63028760719478</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15366195618603</v>
+        <v>73.76390940364233</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251081583252303</v>
+        <v>1.603563247905268</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.936628367580462</v>
+        <v>2.585923452986099</v>
       </c>
       <c r="C2" t="n">
-        <v>4.862596379134452</v>
+        <v>4.356014563743098</v>
       </c>
       <c r="D2" t="n">
-        <v>20.29272504678157</v>
+        <v>13.63353036887546</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.97642235956485</v>
+        <v>8.05523991334508</v>
       </c>
       <c r="C3" t="n">
-        <v>17.20021977840412</v>
+        <v>31.54846247597125</v>
       </c>
       <c r="D3" t="n">
-        <v>40.51672775426587</v>
+        <v>29.72732048459342</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.03817465394117</v>
+        <v>13.33704256219292</v>
       </c>
       <c r="C4" t="n">
-        <v>30.32422308877548</v>
+        <v>75.18518443433348</v>
       </c>
       <c r="D4" t="n">
-        <v>26.99315312826605</v>
+        <v>25.80622015383166</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.98423528346982</v>
+        <v>5.59596191420682</v>
       </c>
       <c r="C5" t="n">
-        <v>16.12520604225386</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D5" t="n">
-        <v>28.98610096788708</v>
+        <v>26.55627539987623</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.07549676223577</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73668130498685</v>
+        <v>14.84171812785499</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0937559604198</v>
+        <v>87.40122897514608</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021004391496053</v>
+        <v>2.473619687975833</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.444993751931063</v>
+        <v>2.994330497952772</v>
       </c>
       <c r="C2" t="n">
-        <v>8.69239417340126</v>
+        <v>6.595381077130072</v>
       </c>
       <c r="D2" t="n">
-        <v>18.8083225179604</v>
+        <v>12.91489104936679</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.08303194870025</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="C3" t="n">
-        <v>18.15742379004476</v>
+        <v>22.56547098211294</v>
       </c>
       <c r="D3" t="n">
-        <v>46.92754026299754</v>
+        <v>33.7328511179204</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.82419471214436</v>
+        <v>14.83028082035232</v>
       </c>
       <c r="C4" t="n">
-        <v>37.13951565165684</v>
+        <v>77.55905038320228</v>
       </c>
       <c r="D4" t="n">
-        <v>40.20256848890688</v>
+        <v>34.65078522139117</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.87029579651497</v>
+        <v>13.27813769993811</v>
       </c>
       <c r="C5" t="n">
-        <v>38.04272353956391</v>
+        <v>91.91612881010764</v>
       </c>
       <c r="D5" t="n">
-        <v>32.2749557771139</v>
+        <v>30.16419821298325</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.4503444588088</v>
+        <v>6.158503348740243</v>
       </c>
       <c r="C6" t="n">
-        <v>19.24029150782899</v>
+        <v>28.57867567062465</v>
       </c>
       <c r="D6" t="n">
-        <v>37.99756314516856</v>
+        <v>33.77113927838603</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06525706963169</v>
+        <v>16.08572306242074</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8542961209306</v>
+        <v>101.5940403942363</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882002693193026</v>
+        <v>3.386468013141209</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.922524046822513</v>
+        <v>2.564325003492669</v>
       </c>
       <c r="C2" t="n">
-        <v>14.2343599638745</v>
+        <v>10.84242164570177</v>
       </c>
       <c r="D2" t="n">
-        <v>22.4535517438288</v>
+        <v>19.00958079733099</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.04161861867264</v>
+        <v>9.508226515630358</v>
       </c>
       <c r="C3" t="n">
-        <v>25.46653544816226</v>
+        <v>24.30316441862979</v>
       </c>
       <c r="D3" t="n">
-        <v>47.78166076569227</v>
+        <v>36.04486696142165</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.88203571123692</v>
+        <v>15.90234931338984</v>
       </c>
       <c r="C4" t="n">
-        <v>34.68907338185679</v>
+        <v>65.03882191094269</v>
       </c>
       <c r="D4" t="n">
-        <v>46.69879304790803</v>
+        <v>43.26562132615693</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.29887757491431</v>
+        <v>17.79417713947344</v>
       </c>
       <c r="C5" t="n">
-        <v>40.71798603363646</v>
+        <v>120.215006385022</v>
       </c>
       <c r="D5" t="n">
-        <v>32.0295188510522</v>
+        <v>35.2447425824605</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.66418553188536</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="C6" t="n">
-        <v>27.45162930614931</v>
+        <v>90.4052190932718</v>
       </c>
       <c r="D6" t="n">
-        <v>30.83276839957533</v>
+        <v>35.98498035146259</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.407867265618931</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>15.86995163914969</v>
+        <v>30.00319158948677</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.062171855391171</v>
+        <v>17.35570390703836</v>
       </c>
       <c r="C21" t="n">
-        <v>66.20786114429222</v>
+        <v>115.4154309818051</v>
       </c>
       <c r="D21" t="n">
-        <v>5.296628891543378</v>
+        <v>4.338925976759589</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.309512568745003</v>
+        <v>2.6467918106494</v>
       </c>
       <c r="C2" t="n">
-        <v>8.462665210607506</v>
+        <v>7.610508203321274</v>
       </c>
       <c r="D2" t="n">
-        <v>20.76690918793278</v>
+        <v>24.4985322117749</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.26237298340793</v>
+        <v>9.046805094634356</v>
       </c>
       <c r="C3" t="n">
-        <v>45.23893421169302</v>
+        <v>33.9488356128547</v>
       </c>
       <c r="D3" t="n">
-        <v>55.53746762924207</v>
+        <v>42.05807164993336</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.10497455555895</v>
+        <v>16.98718052658256</v>
       </c>
       <c r="C4" t="n">
-        <v>53.33540752861647</v>
+        <v>62.74153228300516</v>
       </c>
       <c r="D4" t="n">
-        <v>61.64393834965723</v>
+        <v>50.66799901617789</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.20823799095412</v>
+        <v>20.88668240785089</v>
       </c>
       <c r="C5" t="n">
-        <v>55.32148313430778</v>
+        <v>120.0922879219911</v>
       </c>
       <c r="D5" t="n">
-        <v>42.68148144213009</v>
+        <v>41.65064635267094</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.42396044398116</v>
+        <v>17.75098024048658</v>
       </c>
       <c r="C6" t="n">
-        <v>49.75104666041137</v>
+        <v>138.7877094539631</v>
       </c>
       <c r="D6" t="n">
-        <v>34.25415914887547</v>
+        <v>39.04410619789565</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.13323995033708</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="C7" t="n">
-        <v>30.00319158948677</v>
+        <v>79.11021175591222</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>20.5283444958008</v>
+        <v>32.62838495064274</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>43.56014563743098</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.40561033723673</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.286217852936552</v>
+        <v>17.75629909325389</v>
       </c>
       <c r="C21" t="n">
-        <v>75.59451022421673</v>
+        <v>128.7331684260907</v>
       </c>
       <c r="D21" t="n">
-        <v>6.375440621319483</v>
+        <v>5.326889727976167</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.407867265618932</v>
+        <v>2.410190613925919</v>
       </c>
       <c r="C2" t="n">
-        <v>5.862997289761952</v>
+        <v>4.687845287778519</v>
       </c>
       <c r="D2" t="n">
-        <v>31.59165937495811</v>
+        <v>19.17156916853171</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.43279617331937</v>
+        <v>11.80551614356789</v>
       </c>
       <c r="C3" t="n">
-        <v>37.77765165941727</v>
+        <v>47.69821221083129</v>
       </c>
       <c r="D3" t="n">
-        <v>59.26320016685872</v>
+        <v>47.92892292132928</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.17025293012475</v>
+        <v>10.03149804199391</v>
       </c>
       <c r="C4" t="n">
-        <v>88.63709147792328</v>
+        <v>99.08975928503907</v>
       </c>
       <c r="D4" t="n">
-        <v>75.6574050800762</v>
+        <v>48.88121819444869</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.30827844579606</v>
+        <v>9.989282890711298</v>
       </c>
       <c r="C5" t="n">
-        <v>79.47247665877931</v>
+        <v>82.93313731624932</v>
       </c>
       <c r="D5" t="n">
-        <v>54.8060655895782</v>
+        <v>35.71107274197773</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.85543071223103</v>
+        <v>6.601271563355554</v>
       </c>
       <c r="C6" t="n">
-        <v>71.16492758544281</v>
+        <v>52.08564270111029</v>
       </c>
       <c r="D6" t="n">
-        <v>40.29190752999335</v>
+        <v>25.39879485656924</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.63146906247572</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="C7" t="n">
-        <v>53.23919625360028</v>
+        <v>22.93657161431823</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>31.29320807286708</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>25.07187287105504</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>35.12202411942965</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>33.80157345721769</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.496741852939254</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.275438577184</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.496741852939254</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
